--- a/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
+++ b/data/proteomics/ProMassRatio_across_compartment_NCB_yeast_IO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3286,83 +3286,83 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fungal-type vacuole membrane</t>
+          <t>exocyst</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01908187332084683</v>
+        <v>0.0005358552803275895</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01902883137088115</v>
+        <v>0.0001564236121904053</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01942320800825635</v>
+        <v>0.0001442856721804715</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01906808914300222</v>
+        <v>0.0001441724549679989</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0199934774960193</v>
+        <v>0.0001362805261861699</v>
       </c>
       <c r="H34" t="n">
-        <v>0.02115591123505556</v>
+        <v>0.0001229470533522</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01872948600524103</v>
+        <v>0.0002021865890156859</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0179345663172969</v>
+        <v>0.0001826764805126227</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02149649824966799</v>
+        <v>0.0001558747293563153</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02079029483327808</v>
+        <v>0.0001227177942065366</v>
       </c>
       <c r="M34" t="n">
-        <v>0.02122891833815556</v>
+        <v>0.0001259246056764969</v>
       </c>
       <c r="N34" t="n">
-        <v>0.01906723711262136</v>
+        <v>0.0002105553385782701</v>
       </c>
       <c r="O34" t="n">
-        <v>0.02023210088634203</v>
+        <v>0.0001863813086696067</v>
       </c>
       <c r="P34" t="n">
-        <v>0.02162220008038347</v>
+        <v>0.0001684234496991149</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0232269353732646</v>
+        <v>0.0001100378730097574</v>
       </c>
       <c r="R34" t="n">
-        <v>0.021456399357416</v>
+        <v>0.0001087225727568928</v>
       </c>
       <c r="S34" t="n">
-        <v>0.02080134741754756</v>
+        <v>0.0001117027209118978</v>
       </c>
       <c r="T34" t="n">
-        <v>0.02060626389498114</v>
+        <v>9.195590900802983e-05</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02027698709088437</v>
+        <v>0.0001054649564072733</v>
       </c>
       <c r="V34" t="n">
-        <v>0.01525388642724879</v>
+        <v>9.794891237208528e-05</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01454929481516233</v>
+        <v>0.0001071086225724139</v>
       </c>
       <c r="X34" t="n">
-        <v>0.01417999466744592</v>
+        <v>0.0001032179266097374</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.0148544315493773</v>
+        <v>0.0001017231737686864</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.01507444696697288</v>
+        <v>9.910277861267969e-05</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.01525460568676031</v>
+        <v>0.000104380261914598</v>
       </c>
     </row>
     <row r="35">
@@ -3371,83 +3371,83 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>exocyst</t>
+          <t>mitochondrial intermembrane space</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0005358552803275895</v>
+        <v>0.01508399365546093</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001564236121904053</v>
+        <v>0.01637008914601962</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001442856721804715</v>
+        <v>0.01694578169531561</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0001441724549679989</v>
+        <v>0.01362261136412659</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001362805261861699</v>
+        <v>0.01350540852031208</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0001229470533522</v>
+        <v>0.01461752080519475</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0002021865890156859</v>
+        <v>0.01730239581240865</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0001826764805126227</v>
+        <v>0.01519691628720499</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0001558747293563153</v>
+        <v>0.01564415745771047</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0001227177942065366</v>
+        <v>0.01405315616284072</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0001259246056764969</v>
+        <v>0.01487209578149162</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0002105553385782701</v>
+        <v>0.0197732627550588</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0001863813086696067</v>
+        <v>0.01991555885813889</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0001684234496991149</v>
+        <v>0.01846022365273748</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0001100378730097574</v>
+        <v>0.01582511853423322</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001087225727568928</v>
+        <v>0.01552304955913298</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0001117027209118978</v>
+        <v>0.01474801591437005</v>
       </c>
       <c r="T35" t="n">
-        <v>9.195590900802983e-05</v>
+        <v>0.0165112640289957</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0001054649564072733</v>
+        <v>0.01712235687374338</v>
       </c>
       <c r="V35" t="n">
-        <v>9.794891237208528e-05</v>
+        <v>0.02634707182245907</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0001071086225724139</v>
+        <v>0.0232572908617667</v>
       </c>
       <c r="X35" t="n">
-        <v>0.0001032179266097374</v>
+        <v>0.02019962203923107</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.0001017231737686864</v>
+        <v>0.02417200706066209</v>
       </c>
       <c r="Z35" t="n">
-        <v>9.910277861267969e-05</v>
+        <v>0.0234246845044485</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.000104380261914598</v>
+        <v>0.02264932722265593</v>
       </c>
     </row>
     <row r="36">
@@ -3456,83 +3456,83 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mitochondrial intermembrane space</t>
+          <t>cytoskeleton</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01508399365546093</v>
+        <v>0.02281471274315833</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01637008914601962</v>
+        <v>0.02381715551462424</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01694578169531561</v>
+        <v>0.02380434838754142</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01362261136412659</v>
+        <v>0.02311097930236277</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01350540852031208</v>
+        <v>0.02346836956264856</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01461752080519475</v>
+        <v>0.02447363399974994</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01730239581240865</v>
+        <v>0.0243785448016635</v>
       </c>
       <c r="J36" t="n">
-        <v>0.01519691628720499</v>
+        <v>0.02317180460265634</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01564415745771047</v>
+        <v>0.0258188582921599</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01405315616284072</v>
+        <v>0.02356694336730471</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01487209578149162</v>
+        <v>0.02403745166511074</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0197732627550588</v>
+        <v>0.02516305405529549</v>
       </c>
       <c r="O36" t="n">
-        <v>0.01991555885813889</v>
+        <v>0.02635198781360936</v>
       </c>
       <c r="P36" t="n">
-        <v>0.01846022365273748</v>
+        <v>0.02619838690294803</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.01582511853423322</v>
+        <v>0.02723040269452525</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01552304955913298</v>
+        <v>0.02428271505022495</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01474801591437005</v>
+        <v>0.02415492439113166</v>
       </c>
       <c r="T36" t="n">
-        <v>0.0165112640289957</v>
+        <v>0.02458862623705135</v>
       </c>
       <c r="U36" t="n">
-        <v>0.01712235687374338</v>
+        <v>0.02416119874260546</v>
       </c>
       <c r="V36" t="n">
-        <v>0.02634707182245907</v>
+        <v>0.01844975047797518</v>
       </c>
       <c r="W36" t="n">
-        <v>0.0232572908617667</v>
+        <v>0.01721241742955173</v>
       </c>
       <c r="X36" t="n">
-        <v>0.02019962203923107</v>
+        <v>0.0169037856700798</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.02417200706066209</v>
+        <v>0.01847503588809036</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.0234246845044485</v>
+        <v>0.01912097497019117</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.02264932722265593</v>
+        <v>0.01891677542968843</v>
       </c>
     </row>
     <row r="37">
@@ -3541,83 +3541,83 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cytoskeleton</t>
+          <t>membrane coat</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.02281471274315833</v>
+        <v>0.001553531056830932</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02381715551462424</v>
+        <v>0.00176151512212076</v>
       </c>
       <c r="E37" t="n">
-        <v>0.02380434838754142</v>
+        <v>0.001761553057342448</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02311097930236277</v>
+        <v>0.001867731295480585</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02346836956264856</v>
+        <v>0.001766839867063237</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02447363399974994</v>
+        <v>0.001595822172699758</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0243785448016635</v>
+        <v>0.001679545114739364</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02317180460265634</v>
+        <v>0.001752443150899629</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0258188582921599</v>
+        <v>0.001530933129963779</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02356694336730471</v>
+        <v>0.001520403503109214</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02403745166511074</v>
+        <v>0.001413623151104241</v>
       </c>
       <c r="N37" t="n">
-        <v>0.02516305405529549</v>
+        <v>0.001611530577962683</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02635198781360936</v>
+        <v>0.001628393954067831</v>
       </c>
       <c r="P37" t="n">
-        <v>0.02619838690294803</v>
+        <v>0.001617300861310628</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.02723040269452525</v>
+        <v>0.00157545646423907</v>
       </c>
       <c r="R37" t="n">
-        <v>0.02428271505022495</v>
+        <v>0.001575657836600274</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02415492439113166</v>
+        <v>0.001841986978793295</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02458862623705135</v>
+        <v>0.001311099693658838</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02416119874260546</v>
+        <v>0.001796288690761512</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01844975047797518</v>
+        <v>0.0007349084811016817</v>
       </c>
       <c r="W37" t="n">
-        <v>0.01721241742955173</v>
+        <v>0.0008320626608471476</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0169037856700798</v>
+        <v>0.001003698432221728</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.01847503588809036</v>
+        <v>0.002306200133704163</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.01912097497019117</v>
+        <v>0.002110167209134916</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.01891677542968843</v>
+        <v>0.002139999681020392</v>
       </c>
     </row>
     <row r="38">
@@ -3626,83 +3626,83 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>membrane coat</t>
+          <t>signal recognition particle, endoplasmic reticulum targeting</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001553531056830932</v>
+        <v>0.0006242790074095641</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00176151512212076</v>
+        <v>0.0005721518101955992</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001761553057342448</v>
+        <v>0.0005330777734479101</v>
       </c>
       <c r="F38" t="n">
-        <v>0.001867731295480585</v>
+        <v>0.0005328555719259343</v>
       </c>
       <c r="G38" t="n">
-        <v>0.001766839867063237</v>
+        <v>0.000499071728988123</v>
       </c>
       <c r="H38" t="n">
-        <v>0.001595822172699758</v>
+        <v>0.0004966432980748952</v>
       </c>
       <c r="I38" t="n">
-        <v>0.001679545114739364</v>
+        <v>0.0005865207588275955</v>
       </c>
       <c r="J38" t="n">
-        <v>0.001752443150899629</v>
+        <v>0.0006312851355524271</v>
       </c>
       <c r="K38" t="n">
-        <v>0.001530933129963779</v>
+        <v>0.0005521949008953983</v>
       </c>
       <c r="L38" t="n">
-        <v>0.001520403503109214</v>
+        <v>0.0005369689281804221</v>
       </c>
       <c r="M38" t="n">
-        <v>0.001413623151104241</v>
+        <v>0.0004971973656776743</v>
       </c>
       <c r="N38" t="n">
-        <v>0.001611530577962683</v>
+        <v>0.0005864971531581242</v>
       </c>
       <c r="O38" t="n">
-        <v>0.001628393954067831</v>
+        <v>0.0005291925298866487</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001617300861310628</v>
+        <v>0.0005262755820257572</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.00157545646423907</v>
+        <v>0.0004715925447441128</v>
       </c>
       <c r="R38" t="n">
-        <v>0.001575657836600274</v>
+        <v>0.0004839540120509337</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001841986978793295</v>
+        <v>0.0005635577315482231</v>
       </c>
       <c r="T38" t="n">
-        <v>0.001311099693658838</v>
+        <v>0.0005060485638382923</v>
       </c>
       <c r="U38" t="n">
-        <v>0.001796288690761512</v>
+        <v>0.0005226794556385891</v>
       </c>
       <c r="V38" t="n">
-        <v>0.0007349084811016817</v>
+        <v>0.0003823049272039463</v>
       </c>
       <c r="W38" t="n">
-        <v>0.0008320626608471476</v>
+        <v>0.0003878460790721395</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001003698432221728</v>
+        <v>0.0003597828767549655</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.002306200133704163</v>
+        <v>0.0003647592969705018</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.002110167209134916</v>
+        <v>0.0003672004321527246</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.002139999681020392</v>
+        <v>0.0003668631298687453</v>
       </c>
     </row>
     <row r="39">
@@ -3711,83 +3711,83 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>signal recognition particle, endoplasmic reticulum targeting</t>
+          <t>lipid droplet</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0006242790074095641</v>
+        <v>0.002390574143078394</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0005721518101955992</v>
+        <v>0.002266580524796522</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0005330777734479101</v>
+        <v>0.00218335137297233</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0005328555719259343</v>
+        <v>0.002515791375831853</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000499071728988123</v>
+        <v>0.002348124628596131</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0004966432980748952</v>
+        <v>0.002224318834712633</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0005865207588275955</v>
+        <v>0.002818022775197373</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0006312851355524271</v>
+        <v>0.003358865750441088</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0005521949008953983</v>
+        <v>0.003124622811717728</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0005369689281804221</v>
+        <v>0.002442584673613954</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0004971973656776743</v>
+        <v>0.002075610831720325</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0005864971531581242</v>
+        <v>0.002424246968614171</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0005291925298866487</v>
+        <v>0.002426521769785883</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0005262755820257572</v>
+        <v>0.002583444849959664</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0004715925447441128</v>
+        <v>0.002211288251475335</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0004839540120509337</v>
+        <v>0.002107949085476611</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0005635577315482231</v>
+        <v>0.002436464482216526</v>
       </c>
       <c r="T39" t="n">
-        <v>0.0005060485638382923</v>
+        <v>0.002537433817453647</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0005226794556385891</v>
+        <v>0.00251342759556069</v>
       </c>
       <c r="V39" t="n">
-        <v>0.0003823049272039463</v>
+        <v>0.002168086095835519</v>
       </c>
       <c r="W39" t="n">
-        <v>0.0003878460790721395</v>
+        <v>0.002068342362041124</v>
       </c>
       <c r="X39" t="n">
-        <v>0.0003597828767549655</v>
+        <v>0.002078140725023682</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.0003647592969705018</v>
+        <v>0.002053170749460632</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.0003672004321527246</v>
+        <v>0.002023306529149495</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0003668631298687453</v>
+        <v>0.00211876610917502</v>
       </c>
     </row>
     <row r="40">
@@ -3796,83 +3796,83 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lipid droplet</t>
+          <t>mitochondrial outer membrane</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.002390574143078394</v>
+        <v>0.01328696579296374</v>
       </c>
       <c r="D40" t="n">
-        <v>0.002266580524796522</v>
+        <v>0.01804307271924572</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00218335137297233</v>
+        <v>0.01735073817281346</v>
       </c>
       <c r="F40" t="n">
-        <v>0.002515791375831853</v>
+        <v>0.01369429715354348</v>
       </c>
       <c r="G40" t="n">
-        <v>0.002348124628596131</v>
+        <v>0.01366070432679144</v>
       </c>
       <c r="H40" t="n">
-        <v>0.002224318834712633</v>
+        <v>0.01160287227098371</v>
       </c>
       <c r="I40" t="n">
-        <v>0.002818022775197373</v>
+        <v>0.01497384515204248</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003358865750441088</v>
+        <v>0.01617600184420684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.003124622811717728</v>
+        <v>0.0141418969304688</v>
       </c>
       <c r="L40" t="n">
-        <v>0.002442584673613954</v>
+        <v>0.01175502913174811</v>
       </c>
       <c r="M40" t="n">
-        <v>0.002075610831720325</v>
+        <v>0.01059121758699045</v>
       </c>
       <c r="N40" t="n">
-        <v>0.002424246968614171</v>
+        <v>0.01855755944731068</v>
       </c>
       <c r="O40" t="n">
-        <v>0.002426521769785883</v>
+        <v>0.01817165980539335</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002583444849959664</v>
+        <v>0.01614431452226108</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002211288251475335</v>
+        <v>0.01326710287746759</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002107949085476611</v>
+        <v>0.01167940471696195</v>
       </c>
       <c r="S40" t="n">
-        <v>0.002436464482216526</v>
+        <v>0.0134941574499653</v>
       </c>
       <c r="T40" t="n">
-        <v>0.002537433817453647</v>
+        <v>0.01417041990490767</v>
       </c>
       <c r="U40" t="n">
-        <v>0.00251342759556069</v>
+        <v>0.01397814870584521</v>
       </c>
       <c r="V40" t="n">
-        <v>0.002168086095835519</v>
+        <v>0.01049654003002168</v>
       </c>
       <c r="W40" t="n">
-        <v>0.002068342362041124</v>
+        <v>0.009736733142461387</v>
       </c>
       <c r="X40" t="n">
-        <v>0.002078140725023682</v>
+        <v>0.009923313939468624</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.002053170749460632</v>
+        <v>0.01348122062725029</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.002023306529149495</v>
+        <v>0.01411694162136326</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.00211876610917502</v>
+        <v>0.01385243021619142</v>
       </c>
     </row>
     <row r="41">
@@ -3881,83 +3881,83 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mitochondrial outer membrane</t>
+          <t>endomembrane system</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01328696579296374</v>
+        <v>0.001809466159075253</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01804307271924572</v>
+        <v>0.002100350357250732</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01735073817281346</v>
+        <v>0.002084584789562575</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01369429715354348</v>
+        <v>0.001539217120350638</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01366070432679144</v>
+        <v>0.001487308036916233</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01160287227098371</v>
+        <v>0.001328472366767653</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01497384515204248</v>
+        <v>0.002582129059203324</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01617600184420684</v>
+        <v>0.002647573740805187</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0141418969304688</v>
+        <v>0.00213448400982896</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01175502913174811</v>
+        <v>0.001603882687127571</v>
       </c>
       <c r="M41" t="n">
-        <v>0.01059121758699045</v>
+        <v>0.001345251813673556</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01855755944731068</v>
+        <v>0.002717573858508087</v>
       </c>
       <c r="O41" t="n">
-        <v>0.01817165980539335</v>
+        <v>0.002229508978000917</v>
       </c>
       <c r="P41" t="n">
-        <v>0.01614431452226108</v>
+        <v>0.002020599882111172</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.01326710287746759</v>
+        <v>0.001352369813138702</v>
       </c>
       <c r="R41" t="n">
-        <v>0.01167940471696195</v>
+        <v>0.001150784680110229</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0134941574499653</v>
+        <v>0.001721520140539001</v>
       </c>
       <c r="T41" t="n">
-        <v>0.01417041990490767</v>
+        <v>0.001930249378077407</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01397814870584521</v>
+        <v>0.001818736596671287</v>
       </c>
       <c r="V41" t="n">
-        <v>0.01049654003002168</v>
+        <v>0.0017543909301442</v>
       </c>
       <c r="W41" t="n">
-        <v>0.009736733142461387</v>
+        <v>0.001669505461334047</v>
       </c>
       <c r="X41" t="n">
-        <v>0.009923313939468624</v>
+        <v>0.001769198841693905</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.01348122062725029</v>
+        <v>0.002061504904884993</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.01411694162136326</v>
+        <v>0.001952718579832023</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01385243021619142</v>
+        <v>0.002022793534512414</v>
       </c>
     </row>
     <row r="42">
@@ -3966,83 +3966,83 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>endomembrane system</t>
+          <t>phagophore assembly site</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001809466159075253</v>
+        <v>0.0002723210297339021</v>
       </c>
       <c r="D42" t="n">
-        <v>0.002100350357250732</v>
+        <v>3.394856677788474e-05</v>
       </c>
       <c r="E42" t="n">
-        <v>0.002084584789562575</v>
+        <v>2.652282773981605e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.001539217120350638</v>
+        <v>3.335267737845412e-05</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001487308036916233</v>
+        <v>2.811950584858371e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>0.001328472366767653</v>
+        <v>2.071497817707136e-05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.002582129059203324</v>
+        <v>3.910532441718588e-05</v>
       </c>
       <c r="J42" t="n">
-        <v>0.002647573740805187</v>
+        <v>4.597587394964331e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00213448400982896</v>
+        <v>2.707237751019904e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>0.001603882687127571</v>
+        <v>2.379909996823721e-05</v>
       </c>
       <c r="M42" t="n">
-        <v>0.001345251813673556</v>
+        <v>2.405991436795703e-05</v>
       </c>
       <c r="N42" t="n">
-        <v>0.002717573858508087</v>
+        <v>4.424370669786903e-05</v>
       </c>
       <c r="O42" t="n">
-        <v>0.002229508978000917</v>
+        <v>3.743698822463583e-05</v>
       </c>
       <c r="P42" t="n">
-        <v>0.002020599882111172</v>
+        <v>2.967926812074701e-05</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.001352369813138702</v>
+        <v>2.026848795934809e-05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.001150784680110229</v>
+        <v>1.814977548357987e-05</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001721520140539001</v>
+        <v>0.0001861557087775314</v>
       </c>
       <c r="T42" t="n">
-        <v>0.001930249378077407</v>
+        <v>0.0001829177799781372</v>
       </c>
       <c r="U42" t="n">
-        <v>0.001818736596671287</v>
+        <v>0.0001836103781884727</v>
       </c>
       <c r="V42" t="n">
-        <v>0.0017543909301442</v>
+        <v>0.0001449947622227811</v>
       </c>
       <c r="W42" t="n">
-        <v>0.001669505461334047</v>
+        <v>0.0001392457965362703</v>
       </c>
       <c r="X42" t="n">
-        <v>0.001769198841693905</v>
+        <v>0.0001241356466068114</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.002061504904884993</v>
+        <v>0.0001718533709911829</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.001952718579832023</v>
+        <v>0.0001885425508596839</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.002022793534512414</v>
+        <v>0.0001982074529014195</v>
       </c>
     </row>
     <row r="43">
@@ -4051,83 +4051,83 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>phagophore assembly site</t>
+          <t>peroxisomal membrane</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0002723210297339021</v>
+        <v>0.0002495375593337997</v>
       </c>
       <c r="D43" t="n">
-        <v>3.394856677788474e-05</v>
+        <v>0.0001518177018418605</v>
       </c>
       <c r="E43" t="n">
-        <v>2.652282773981605e-05</v>
+        <v>0.0001222465108365021</v>
       </c>
       <c r="F43" t="n">
-        <v>3.335267737845412e-05</v>
+        <v>9.695501375888201e-05</v>
       </c>
       <c r="G43" t="n">
-        <v>2.811950584858371e-05</v>
+        <v>0.0001002783737663621</v>
       </c>
       <c r="H43" t="n">
-        <v>2.071497817707136e-05</v>
+        <v>7.940709427198587e-05</v>
       </c>
       <c r="I43" t="n">
-        <v>3.910532441718588e-05</v>
+        <v>0.0001538884082265994</v>
       </c>
       <c r="J43" t="n">
-        <v>4.597587394964331e-05</v>
+        <v>0.0001608067975259784</v>
       </c>
       <c r="K43" t="n">
-        <v>2.707237751019904e-05</v>
+        <v>0.0001219078868951301</v>
       </c>
       <c r="L43" t="n">
-        <v>2.379909996823721e-05</v>
+        <v>8.991351339912702e-05</v>
       </c>
       <c r="M43" t="n">
-        <v>2.405991436795703e-05</v>
+        <v>8.297315928684663e-05</v>
       </c>
       <c r="N43" t="n">
-        <v>4.424370669786903e-05</v>
+        <v>0.0001764020391878214</v>
       </c>
       <c r="O43" t="n">
-        <v>3.743698822463583e-05</v>
+        <v>0.0001529979043404599</v>
       </c>
       <c r="P43" t="n">
-        <v>2.967926812074701e-05</v>
+        <v>0.0001230710744108388</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.026848795934809e-05</v>
+        <v>9.029230184585892e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.814977548357987e-05</v>
+        <v>7.487542011458173e-05</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0001861557087775314</v>
+        <v>0.0001326659899018738</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0001829177799781372</v>
+        <v>0.0001288941714234372</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0001836103781884727</v>
+        <v>0.0001256652854047475</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0001449947622227811</v>
+        <v>0.000112491054953251</v>
       </c>
       <c r="W43" t="n">
-        <v>0.0001392457965362703</v>
+        <v>0.0001126482111588829</v>
       </c>
       <c r="X43" t="n">
-        <v>0.0001241356466068114</v>
+        <v>0.0001223252106743743</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.0001718533709911829</v>
+        <v>0.0001485692645769183</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.0001885425508596839</v>
+        <v>0.0001338380175065627</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0001982074529014195</v>
+        <v>0.0001187776543722757</v>
       </c>
     </row>
     <row r="44">
@@ -4136,83 +4136,83 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>peroxisomal membrane</t>
+          <t>fungal-type cell wall</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0002495375593337997</v>
+        <v>0.005983680466147395</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001518177018418605</v>
+        <v>0.007652764228742905</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001222465108365021</v>
+        <v>0.007223864627721767</v>
       </c>
       <c r="F44" t="n">
-        <v>9.695501375888201e-05</v>
+        <v>0.00535333774296065</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0001002783737663621</v>
+        <v>0.005031748096672706</v>
       </c>
       <c r="H44" t="n">
-        <v>7.940709427198587e-05</v>
+        <v>0.005404788429659431</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0001538884082265994</v>
+        <v>0.007188822473926021</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0001608067975259784</v>
+        <v>0.006457729417798598</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0001219078868951301</v>
+        <v>0.005824096056265674</v>
       </c>
       <c r="L44" t="n">
-        <v>8.991351339912702e-05</v>
+        <v>0.004664178986384286</v>
       </c>
       <c r="M44" t="n">
-        <v>8.297315928684663e-05</v>
+        <v>0.004850190902417942</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0001764020391878214</v>
+        <v>0.008681667488353664</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0001529979043404599</v>
+        <v>0.007518172001187375</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0001230710744108388</v>
+        <v>0.006789988993074297</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.029230184585892e-05</v>
+        <v>0.005473718544289317</v>
       </c>
       <c r="R44" t="n">
-        <v>7.487542011458173e-05</v>
+        <v>0.004851945344999886</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0001326659899018738</v>
+        <v>0.005947656903728151</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0001288941714234372</v>
+        <v>0.006449942415829216</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0001256652854047475</v>
+        <v>0.006255106572380834</v>
       </c>
       <c r="V44" t="n">
-        <v>0.000112491054953251</v>
+        <v>0.007159449806872925</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0001126482111588829</v>
+        <v>0.006800360382374504</v>
       </c>
       <c r="X44" t="n">
-        <v>0.0001223252106743743</v>
+        <v>0.007741706598532338</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0001485692645769183</v>
+        <v>0.005434433088065333</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0001338380175065627</v>
+        <v>0.00551845361634321</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0001187776543722757</v>
+        <v>0.005342563044460486</v>
       </c>
     </row>
     <row r="45">
@@ -4221,83 +4221,83 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fungal-type cell wall</t>
+          <t>extracellular region</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.005983680466147395</v>
+        <v>0.001452739667808176</v>
       </c>
       <c r="D45" t="n">
-        <v>0.007652764228742905</v>
+        <v>0.001149646641332225</v>
       </c>
       <c r="E45" t="n">
-        <v>0.007223864627721767</v>
+        <v>0.00123179633456214</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00535333774296065</v>
+        <v>0.001080150017724745</v>
       </c>
       <c r="G45" t="n">
-        <v>0.005031748096672706</v>
+        <v>0.001014266311319326</v>
       </c>
       <c r="H45" t="n">
-        <v>0.005404788429659431</v>
+        <v>0.0009839775000656428</v>
       </c>
       <c r="I45" t="n">
-        <v>0.007188822473926021</v>
+        <v>0.001249506794871048</v>
       </c>
       <c r="J45" t="n">
-        <v>0.006457729417798598</v>
+        <v>0.001142274377704156</v>
       </c>
       <c r="K45" t="n">
-        <v>0.005824096056265674</v>
+        <v>0.001041675630876567</v>
       </c>
       <c r="L45" t="n">
-        <v>0.004664178986384286</v>
+        <v>0.0008347477191458009</v>
       </c>
       <c r="M45" t="n">
-        <v>0.004850190902417942</v>
+        <v>0.0007810998401648865</v>
       </c>
       <c r="N45" t="n">
-        <v>0.008681667488353664</v>
+        <v>0.001920422607984662</v>
       </c>
       <c r="O45" t="n">
-        <v>0.007518172001187375</v>
+        <v>0.001610814391763438</v>
       </c>
       <c r="P45" t="n">
-        <v>0.006789988993074297</v>
+        <v>0.001362735581137217</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.005473718544289317</v>
+        <v>0.0008873404395304387</v>
       </c>
       <c r="R45" t="n">
-        <v>0.004851945344999886</v>
+        <v>0.0008350195093170825</v>
       </c>
       <c r="S45" t="n">
-        <v>0.005947656903728151</v>
+        <v>0.001351253138138688</v>
       </c>
       <c r="T45" t="n">
-        <v>0.006449942415829216</v>
+        <v>0.001445904089431632</v>
       </c>
       <c r="U45" t="n">
-        <v>0.006255106572380834</v>
+        <v>0.001383190103036292</v>
       </c>
       <c r="V45" t="n">
-        <v>0.007159449806872925</v>
+        <v>0.0009035649277458336</v>
       </c>
       <c r="W45" t="n">
-        <v>0.006800360382374504</v>
+        <v>0.0009140976316984115</v>
       </c>
       <c r="X45" t="n">
-        <v>0.007741706598532338</v>
+        <v>0.0008428889528889499</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.005434433088065333</v>
+        <v>0.001356872149918086</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.00551845361634321</v>
+        <v>0.001225131722638809</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.005342563044460486</v>
+        <v>0.001570283624791493</v>
       </c>
     </row>
     <row r="46">
@@ -4306,83 +4306,83 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>extracellular region</t>
+          <t>p-body</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001452739667808176</v>
+        <v>0.002841211206084643</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001149646641332225</v>
+        <v>0.00270293426045726</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00123179633456214</v>
+        <v>0.002574475201064284</v>
       </c>
       <c r="F46" t="n">
-        <v>0.001080150017724745</v>
+        <v>0.002600375463790951</v>
       </c>
       <c r="G46" t="n">
-        <v>0.001014266311319326</v>
+        <v>0.002483989837425312</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0009839775000656428</v>
+        <v>0.002457573923601113</v>
       </c>
       <c r="I46" t="n">
-        <v>0.001249506794871048</v>
+        <v>0.00291019760970828</v>
       </c>
       <c r="J46" t="n">
-        <v>0.001142274377704156</v>
+        <v>0.002988499454207387</v>
       </c>
       <c r="K46" t="n">
-        <v>0.001041675630876567</v>
+        <v>0.002643570262820109</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0008347477191458009</v>
+        <v>0.002538337643207652</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0007810998401648865</v>
+        <v>0.002271450734314326</v>
       </c>
       <c r="N46" t="n">
-        <v>0.001920422607984662</v>
+        <v>0.003019501883754756</v>
       </c>
       <c r="O46" t="n">
-        <v>0.001610814391763438</v>
+        <v>0.002847709046853142</v>
       </c>
       <c r="P46" t="n">
-        <v>0.001362735581137217</v>
+        <v>0.002657080580107464</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0008873404395304387</v>
+        <v>0.002242213631956188</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0008350195093170825</v>
+        <v>0.002209149495408162</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001351253138138688</v>
+        <v>0.002638555582437114</v>
       </c>
       <c r="T46" t="n">
-        <v>0.001445904089431632</v>
+        <v>0.00251859210200058</v>
       </c>
       <c r="U46" t="n">
-        <v>0.001383190103036292</v>
+        <v>0.002614404761105013</v>
       </c>
       <c r="V46" t="n">
-        <v>0.0009035649277458336</v>
+        <v>0.001979051106497346</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0009140976316984115</v>
+        <v>0.002022895498495056</v>
       </c>
       <c r="X46" t="n">
-        <v>0.0008428889528889499</v>
+        <v>0.001932744359723087</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.001356872149918086</v>
+        <v>0.002030490449973196</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.001225131722638809</v>
+        <v>0.002015136718120107</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.001570283624791493</v>
+        <v>0.002079443787345185</v>
       </c>
     </row>
     <row r="47">
@@ -4391,83 +4391,83 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>p-body</t>
+          <t>endoplasmic reticulum lumen</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002841211206084643</v>
+        <v>0.001933271845497709</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00270293426045726</v>
+        <v>0.001934362209237071</v>
       </c>
       <c r="E47" t="n">
-        <v>0.002574475201064284</v>
+        <v>0.001784870901284783</v>
       </c>
       <c r="F47" t="n">
-        <v>0.002600375463790951</v>
+        <v>0.001885146537167181</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002483989837425312</v>
+        <v>0.001798249607403743</v>
       </c>
       <c r="H47" t="n">
-        <v>0.002457573923601113</v>
+        <v>0.001602492409427728</v>
       </c>
       <c r="I47" t="n">
-        <v>0.00291019760970828</v>
+        <v>0.00185199103132686</v>
       </c>
       <c r="J47" t="n">
-        <v>0.002988499454207387</v>
+        <v>0.002206342927957643</v>
       </c>
       <c r="K47" t="n">
-        <v>0.002643570262820109</v>
+        <v>0.001725727590415853</v>
       </c>
       <c r="L47" t="n">
-        <v>0.002538337643207652</v>
+        <v>0.00159593489639947</v>
       </c>
       <c r="M47" t="n">
-        <v>0.002271450734314326</v>
+        <v>0.001325721205556694</v>
       </c>
       <c r="N47" t="n">
-        <v>0.003019501883754756</v>
+        <v>0.002431977186519194</v>
       </c>
       <c r="O47" t="n">
-        <v>0.002847709046853142</v>
+        <v>0.002405312386316173</v>
       </c>
       <c r="P47" t="n">
-        <v>0.002657080580107464</v>
+        <v>0.002261645553741884</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.002242213631956188</v>
+        <v>0.001880704086332645</v>
       </c>
       <c r="R47" t="n">
-        <v>0.002209149495408162</v>
+        <v>0.001634365954043897</v>
       </c>
       <c r="S47" t="n">
-        <v>0.002638555582437114</v>
+        <v>0.001839490097808482</v>
       </c>
       <c r="T47" t="n">
-        <v>0.00251859210200058</v>
+        <v>0.001819431450827279</v>
       </c>
       <c r="U47" t="n">
-        <v>0.002614404761105013</v>
+        <v>0.001816036052303416</v>
       </c>
       <c r="V47" t="n">
-        <v>0.001979051106497346</v>
+        <v>0.001076966383893888</v>
       </c>
       <c r="W47" t="n">
-        <v>0.002022895498495056</v>
+        <v>0.001076324226578104</v>
       </c>
       <c r="X47" t="n">
-        <v>0.001932744359723087</v>
+        <v>0.001001725216397515</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.002030490449973196</v>
+        <v>0.001372755388180504</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.002015136718120107</v>
+        <v>0.001293049119527377</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.002079443787345185</v>
+        <v>0.001352511552505914</v>
       </c>
     </row>
     <row r="48">
@@ -4476,83 +4476,83 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum lumen</t>
+          <t>chromatin</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.001933271845497709</v>
+        <v>0.005743574581470352</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001934362209237071</v>
+        <v>0.006946400181497864</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001784870901284783</v>
+        <v>0.006438660053091616</v>
       </c>
       <c r="F48" t="n">
-        <v>0.001885146537167181</v>
+        <v>0.006335533885122047</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001798249607403743</v>
+        <v>0.005558692954677638</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001602492409427728</v>
+        <v>0.005357340254273148</v>
       </c>
       <c r="I48" t="n">
-        <v>0.00185199103132686</v>
+        <v>0.00772519803555185</v>
       </c>
       <c r="J48" t="n">
-        <v>0.002206342927957643</v>
+        <v>0.0074020228327254</v>
       </c>
       <c r="K48" t="n">
-        <v>0.001725727590415853</v>
+        <v>0.006335367133608999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.00159593489639947</v>
+        <v>0.00481516166734413</v>
       </c>
       <c r="M48" t="n">
-        <v>0.001325721205556694</v>
+        <v>0.004700721421917206</v>
       </c>
       <c r="N48" t="n">
-        <v>0.002431977186519194</v>
+        <v>0.008152474066774724</v>
       </c>
       <c r="O48" t="n">
-        <v>0.002405312386316173</v>
+        <v>0.007974127470814552</v>
       </c>
       <c r="P48" t="n">
-        <v>0.002261645553741884</v>
+        <v>0.006653803770920588</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.001880704086332645</v>
+        <v>0.005912545845929427</v>
       </c>
       <c r="R48" t="n">
-        <v>0.001634365954043897</v>
+        <v>0.004936142303397</v>
       </c>
       <c r="S48" t="n">
-        <v>0.001839490097808482</v>
+        <v>0.005670761351519421</v>
       </c>
       <c r="T48" t="n">
-        <v>0.001819431450827279</v>
+        <v>0.006153712057993681</v>
       </c>
       <c r="U48" t="n">
-        <v>0.001816036052303416</v>
+        <v>0.005979277542624518</v>
       </c>
       <c r="V48" t="n">
-        <v>0.001076966383893888</v>
+        <v>0.004707904414785332</v>
       </c>
       <c r="W48" t="n">
-        <v>0.001076324226578104</v>
+        <v>0.004170865517642899</v>
       </c>
       <c r="X48" t="n">
-        <v>0.001001725216397515</v>
+        <v>0.004241727885558589</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.001372755388180504</v>
+        <v>0.00529932080986658</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.001293049119527377</v>
+        <v>0.005559611241138992</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.001352511552505914</v>
+        <v>0.005333271931152556</v>
       </c>
     </row>
     <row r="49">
@@ -4561,83 +4561,83 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>chromatin</t>
+          <t>nuclear chromosome</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.005743574581470352</v>
+        <v>0.0002698055205602525</v>
       </c>
       <c r="D49" t="n">
-        <v>0.006946400181497864</v>
+        <v>0.0001677484456963893</v>
       </c>
       <c r="E49" t="n">
-        <v>0.006438660053091616</v>
+        <v>0.0002520913057514608</v>
       </c>
       <c r="F49" t="n">
-        <v>0.006335533885122047</v>
+        <v>0.0002050063882197967</v>
       </c>
       <c r="G49" t="n">
-        <v>0.005558692954677638</v>
+        <v>0.000238753504270567</v>
       </c>
       <c r="H49" t="n">
-        <v>0.005357340254273148</v>
+        <v>0.0001911802331863812</v>
       </c>
       <c r="I49" t="n">
-        <v>0.00772519803555185</v>
+        <v>0.0002717556640291989</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0074020228327254</v>
+        <v>0.0002138998429159144</v>
       </c>
       <c r="K49" t="n">
-        <v>0.006335367133608999</v>
+        <v>0.0001933924140167134</v>
       </c>
       <c r="L49" t="n">
-        <v>0.00481516166734413</v>
+        <v>0.0002002072959548799</v>
       </c>
       <c r="M49" t="n">
-        <v>0.004700721421917206</v>
+        <v>0.0001727007287632688</v>
       </c>
       <c r="N49" t="n">
-        <v>0.008152474066774724</v>
+        <v>0.0002819075325764394</v>
       </c>
       <c r="O49" t="n">
-        <v>0.007974127470814552</v>
+        <v>0.0002195647475135317</v>
       </c>
       <c r="P49" t="n">
-        <v>0.006653803770920588</v>
+        <v>0.0002046074694765401</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.005912545845929427</v>
+        <v>0.0001930656036686228</v>
       </c>
       <c r="R49" t="n">
-        <v>0.004936142303397</v>
+        <v>0.000165842858557824</v>
       </c>
       <c r="S49" t="n">
-        <v>0.005670761351519421</v>
+        <v>0.0001922721668752386</v>
       </c>
       <c r="T49" t="n">
-        <v>0.006153712057993681</v>
+        <v>0.0001742179120644675</v>
       </c>
       <c r="U49" t="n">
-        <v>0.005979277542624518</v>
+        <v>0.0001826651481027825</v>
       </c>
       <c r="V49" t="n">
-        <v>0.004707904414785332</v>
+        <v>0.0001439253413828087</v>
       </c>
       <c r="W49" t="n">
-        <v>0.004170865517642899</v>
+        <v>0.0001371997456188582</v>
       </c>
       <c r="X49" t="n">
-        <v>0.004241727885558589</v>
+        <v>0.0001310114999771917</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.00529932080986658</v>
+        <v>0.000153648774346747</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.005559611241138992</v>
+        <v>0.000134550320905362</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.005333271931152556</v>
+        <v>0.0001451057186716903</v>
       </c>
     </row>
     <row r="50">
@@ -4646,83 +4646,83 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nuclear chromosome</t>
+          <t>perinuclear region of cytoplasm</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0002698055205602525</v>
+        <v>0.002708686274630764</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001677484456963893</v>
+        <v>0.002804920605480554</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002520913057514608</v>
+        <v>0.002995336779127752</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0002050063882197967</v>
+        <v>0.002835996884296331</v>
       </c>
       <c r="G50" t="n">
-        <v>0.000238753504270567</v>
+        <v>0.00316617965409115</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0001911802331863812</v>
+        <v>0.003244037717419838</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0002717556640291989</v>
+        <v>0.002702480150930566</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0002138998429159144</v>
+        <v>0.002499589735192351</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0001933924140167134</v>
+        <v>0.00294645134910494</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0002002072959548799</v>
+        <v>0.002864082281165858</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0001727007287632688</v>
+        <v>0.003259143603294188</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0002819075325764394</v>
+        <v>0.002626759390516757</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0002195647475135317</v>
+        <v>0.002645454291212479</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0002046074694765401</v>
+        <v>0.002769441852923764</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0001930656036686228</v>
+        <v>0.003056729550626399</v>
       </c>
       <c r="R50" t="n">
-        <v>0.000165842858557824</v>
+        <v>0.003081302964947798</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0001922721668752386</v>
+        <v>0.002835299218938386</v>
       </c>
       <c r="T50" t="n">
-        <v>0.0001742179120644675</v>
+        <v>0.003121353384407719</v>
       </c>
       <c r="U50" t="n">
-        <v>0.0001826651481027825</v>
+        <v>0.002909319207624511</v>
       </c>
       <c r="V50" t="n">
-        <v>0.0001439253413828087</v>
+        <v>0.002225139679380553</v>
       </c>
       <c r="W50" t="n">
-        <v>0.0001371997456188582</v>
+        <v>0.002003723161459789</v>
       </c>
       <c r="X50" t="n">
-        <v>0.0001310114999771917</v>
+        <v>0.001887931169369626</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.000153648774346747</v>
+        <v>0.001951953476106176</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.000134550320905362</v>
+        <v>0.001947463703126401</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.0001451057186716903</v>
+        <v>0.001981979311235987</v>
       </c>
     </row>
     <row r="51">
@@ -4731,83 +4731,83 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>perinuclear region of cytoplasm</t>
+          <t>fungal-type vacuole</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.002708686274630764</v>
+        <v>0.007577441363209836</v>
       </c>
       <c r="D51" t="n">
-        <v>0.002804920605480554</v>
+        <v>0.007471113126002135</v>
       </c>
       <c r="E51" t="n">
-        <v>0.002995336779127752</v>
+        <v>0.007500154617183421</v>
       </c>
       <c r="F51" t="n">
-        <v>0.002835996884296331</v>
+        <v>0.007195576236706518</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00316617965409115</v>
+        <v>0.007149396703308463</v>
       </c>
       <c r="H51" t="n">
-        <v>0.003244037717419838</v>
+        <v>0.006943977258985435</v>
       </c>
       <c r="I51" t="n">
-        <v>0.002702480150930566</v>
+        <v>0.008873797521648208</v>
       </c>
       <c r="J51" t="n">
-        <v>0.002499589735192351</v>
+        <v>0.008476823656519871</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00294645134910494</v>
+        <v>0.007930290005887833</v>
       </c>
       <c r="L51" t="n">
-        <v>0.002864082281165858</v>
+        <v>0.007321927626050002</v>
       </c>
       <c r="M51" t="n">
-        <v>0.003259143603294188</v>
+        <v>0.007221707912283871</v>
       </c>
       <c r="N51" t="n">
-        <v>0.002626759390516757</v>
+        <v>0.009656196511012056</v>
       </c>
       <c r="O51" t="n">
-        <v>0.002645454291212479</v>
+        <v>0.009068211451395016</v>
       </c>
       <c r="P51" t="n">
-        <v>0.002769441852923764</v>
+        <v>0.008132294656826172</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.003056729550626399</v>
+        <v>0.006985076173740401</v>
       </c>
       <c r="R51" t="n">
-        <v>0.003081302964947798</v>
+        <v>0.00656532745356324</v>
       </c>
       <c r="S51" t="n">
-        <v>0.002835299218938386</v>
+        <v>0.007959628195158726</v>
       </c>
       <c r="T51" t="n">
-        <v>0.003121353384407719</v>
+        <v>0.007945044830403866</v>
       </c>
       <c r="U51" t="n">
-        <v>0.002909319207624511</v>
+        <v>0.007982990881021661</v>
       </c>
       <c r="V51" t="n">
-        <v>0.002225139679380553</v>
+        <v>0.007906792082448355</v>
       </c>
       <c r="W51" t="n">
-        <v>0.002003723161459789</v>
+        <v>0.008154310259947228</v>
       </c>
       <c r="X51" t="n">
-        <v>0.001887931169369626</v>
+        <v>0.007613276797491796</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.001951953476106176</v>
+        <v>0.007035223649025524</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.001947463703126401</v>
+        <v>0.006754667171083195</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.001981979311235987</v>
+        <v>0.007790061114742422</v>
       </c>
     </row>
     <row r="52">
@@ -4816,83 +4816,83 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fungal-type vacuole</t>
+          <t>nuclear lumen</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.007577441363209836</v>
+        <v>0.000455758775774598</v>
       </c>
       <c r="D52" t="n">
-        <v>0.007471113126002135</v>
+        <v>0.0002553986114568351</v>
       </c>
       <c r="E52" t="n">
-        <v>0.007500154617183421</v>
+        <v>0.000251725280461319</v>
       </c>
       <c r="F52" t="n">
-        <v>0.007195576236706518</v>
+        <v>0.0004543017391719726</v>
       </c>
       <c r="G52" t="n">
-        <v>0.007149396703308463</v>
+        <v>0.0004600600536151387</v>
       </c>
       <c r="H52" t="n">
-        <v>0.006943977258985435</v>
+        <v>0.0004614286923371877</v>
       </c>
       <c r="I52" t="n">
-        <v>0.008873797521648208</v>
+        <v>0.0003112797173334303</v>
       </c>
       <c r="J52" t="n">
-        <v>0.008476823656519871</v>
+        <v>0.0003273848641689844</v>
       </c>
       <c r="K52" t="n">
-        <v>0.007930290005887833</v>
+        <v>0.0003048795791594759</v>
       </c>
       <c r="L52" t="n">
-        <v>0.007321927626050002</v>
+        <v>0.0004327961025919525</v>
       </c>
       <c r="M52" t="n">
-        <v>0.007221707912283871</v>
+        <v>0.0004367001667104378</v>
       </c>
       <c r="N52" t="n">
-        <v>0.009656196511012056</v>
+        <v>0.000332492783303985</v>
       </c>
       <c r="O52" t="n">
-        <v>0.009068211451395016</v>
+        <v>0.0003776290683092197</v>
       </c>
       <c r="P52" t="n">
-        <v>0.008132294656826172</v>
+        <v>0.000380699095895506</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.006985076173740401</v>
+        <v>0.0005029907051687337</v>
       </c>
       <c r="R52" t="n">
-        <v>0.00656532745356324</v>
+        <v>0.0005335674547983937</v>
       </c>
       <c r="S52" t="n">
-        <v>0.007959628195158726</v>
+        <v>0.0004165021237119085</v>
       </c>
       <c r="T52" t="n">
-        <v>0.007945044830403866</v>
+        <v>0.0003527367958098957</v>
       </c>
       <c r="U52" t="n">
-        <v>0.007982990881021661</v>
+        <v>0.0003704793598124509</v>
       </c>
       <c r="V52" t="n">
-        <v>0.007906792082448355</v>
+        <v>0.0002641588153476301</v>
       </c>
       <c r="W52" t="n">
-        <v>0.008154310259947228</v>
+        <v>0.0002784064762593761</v>
       </c>
       <c r="X52" t="n">
-        <v>0.007613276797491796</v>
+        <v>0.000292840085129436</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.007035223649025524</v>
+        <v>0.0003379551179382276</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.006754667171083195</v>
+        <v>0.0003332033454322565</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.007790061114742422</v>
+        <v>0.0003553636312180523</v>
       </c>
     </row>
     <row r="53">
@@ -4901,83 +4901,83 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nuclear lumen</t>
+          <t>kinetochore</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.000455758775774598</v>
+        <v>0.001018564044179966</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0002553986114568351</v>
+        <v>0.000917653579718386</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000251725280461319</v>
+        <v>0.0009114259046707069</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0004543017391719726</v>
+        <v>0.0007891423385227664</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0004600600536151387</v>
+        <v>0.0008189856839072458</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0004614286923371877</v>
+        <v>0.0007222293873727233</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0003112797173334303</v>
+        <v>0.001153861335482152</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0003273848641689844</v>
+        <v>0.001142328588630998</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0003048795791594759</v>
+        <v>0.0009041991152160645</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0004327961025919525</v>
+        <v>0.0007848954237953818</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0004367001667104378</v>
+        <v>0.0007235348293033722</v>
       </c>
       <c r="N53" t="n">
-        <v>0.000332492783303985</v>
+        <v>0.001208518362022733</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0003776290683092197</v>
+        <v>0.001162546775159722</v>
       </c>
       <c r="P53" t="n">
-        <v>0.000380699095895506</v>
+        <v>0.001061828446095393</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.0005029907051687337</v>
+        <v>0.0007233985850834721</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0005335674547983937</v>
+        <v>0.0006892828859902274</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0004165021237119085</v>
+        <v>0.0007444570241469903</v>
       </c>
       <c r="T53" t="n">
-        <v>0.0003527367958098957</v>
+        <v>0.0007707633276665341</v>
       </c>
       <c r="U53" t="n">
-        <v>0.0003704793598124509</v>
+        <v>0.000726074755452486</v>
       </c>
       <c r="V53" t="n">
-        <v>0.0002641588153476301</v>
+        <v>0.0006997694897726436</v>
       </c>
       <c r="W53" t="n">
-        <v>0.0002784064762593761</v>
+        <v>0.0006570802399636368</v>
       </c>
       <c r="X53" t="n">
-        <v>0.000292840085129436</v>
+        <v>0.0007262028570148418</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.0003379551179382276</v>
+        <v>0.0007461346543806114</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.0003332033454322565</v>
+        <v>0.0007185244077124068</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.0003553636312180523</v>
+        <v>0.0007573410081003682</v>
       </c>
     </row>
     <row r="54">
@@ -4986,83 +4986,83 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kinetochore</t>
+          <t>phagophore assembly site membrane</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.001018564044179966</v>
+        <v>0.0002375595765585929</v>
       </c>
       <c r="D54" t="n">
-        <v>0.000917653579718386</v>
+        <v>2.611827845408975e-05</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0009114259046707069</v>
+        <v>2.027747036509249e-05</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0007891423385227664</v>
+        <v>2.539353846625164e-05</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0008189856839072458</v>
+        <v>1.974568889131004e-05</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0007222293873727233</v>
+        <v>1.447738418347844e-05</v>
       </c>
       <c r="I54" t="n">
-        <v>0.001153861335482152</v>
+        <v>3.298411016340228e-05</v>
       </c>
       <c r="J54" t="n">
-        <v>0.001142328588630998</v>
+        <v>3.905884214924494e-05</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0009041991152160645</v>
+        <v>2.143598252013681e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0007848954237953818</v>
+        <v>1.622178958707292e-05</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0007235348293033722</v>
+        <v>1.698443102198877e-05</v>
       </c>
       <c r="N54" t="n">
-        <v>0.001208518362022733</v>
+        <v>3.811238005531212e-05</v>
       </c>
       <c r="O54" t="n">
-        <v>0.001162546775159722</v>
+        <v>3.259357110863686e-05</v>
       </c>
       <c r="P54" t="n">
-        <v>0.001061828446095393</v>
+        <v>2.296402836842546e-05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0007233985850834721</v>
+        <v>1.40849009756898e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0006892828859902274</v>
+        <v>1.248216061110372e-05</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007444570241469903</v>
+        <v>0.0001908656795058409</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0007707633276665341</v>
+        <v>0.0001907120791055339</v>
       </c>
       <c r="U54" t="n">
-        <v>0.000726074755452486</v>
+        <v>0.0001937090222217713</v>
       </c>
       <c r="V54" t="n">
-        <v>0.0006997694897726436</v>
+        <v>0.0001533043975463161</v>
       </c>
       <c r="W54" t="n">
-        <v>0.0006570802399636368</v>
+        <v>0.0001465221765150939</v>
       </c>
       <c r="X54" t="n">
-        <v>0.0007262028570148418</v>
+        <v>0.000135593607607135</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.0007461346543806114</v>
+        <v>0.0001819432428485295</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.0007185244077124068</v>
+        <v>0.0001977926376525092</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.0007573410081003682</v>
+        <v>0.000206010014499834</v>
       </c>
     </row>
     <row r="55">
@@ -5071,83 +5071,83 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>phagophore assembly site membrane</t>
+          <t>bounding membrane of organelle</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.0002375595765585929</v>
+        <v>0.0001010532642216441</v>
       </c>
       <c r="D55" t="n">
-        <v>2.611827845408975e-05</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2.027747036509249e-05</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>2.539353846625164e-05</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.974568889131004e-05</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.447738418347844e-05</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3.298411016340228e-05</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3.905884214924494e-05</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2.143598252013681e-05</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1.622178958707292e-05</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1.698443102198877e-05</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.811238005531212e-05</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.259357110863686e-05</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.296402836842546e-05</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.40849009756898e-05</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.248216061110372e-05</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0001908656795058409</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.0001907120791055339</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0001937090222217713</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0001533043975463161</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.0001465221765150939</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0.000135593607607135</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.0001819432428485295</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.0001977926376525092</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.000206010014499834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5156,83 +5156,83 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bounding membrane of organelle</t>
+          <t>extrinsic component of mitochondrial inner membrane</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.0001010532642216441</v>
+        <v>0.0005088726818011123</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.0004738807507877627</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.0003917948550141327</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.0004897380363753663</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.000458090034732102</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.0004176167585381165</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>0.0003177421123621354</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.0003644454833698056</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.0003237558745760494</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.0004217577979304504</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>0.000368693775630591</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.0004984578215202946</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>0.0004500185738535041</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.0004244644107541152</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.0003695371285443526</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>0.0004344194938406465</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.0005935444491544616</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>0.0005189069753347839</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>0.0005580070907635715</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>0.0005926991665286614</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>0.0005647696334079814</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>0.0005580551416359648</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>0.00071131573563992</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>0.0006801128475512493</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>0.0007898545424566821</v>
       </c>
     </row>
     <row r="57">
@@ -5241,83 +5241,83 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>extrinsic component of mitochondrial inner membrane</t>
+          <t>cellular bud</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.0005088726818011123</v>
+        <v>0.001884614432021933</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0004738807507877627</v>
+        <v>0.002160813469002975</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0003917948550141327</v>
+        <v>0.001899324188642959</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0004897380363753663</v>
+        <v>0.001821548985516648</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000458090034732102</v>
+        <v>0.00169177362184389</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0004176167585381165</v>
+        <v>0.00147503523328639</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0003177421123621354</v>
+        <v>0.002371854233116223</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0003644454833698056</v>
+        <v>0.002475654425363569</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0003237558745760494</v>
+        <v>0.002030531077052462</v>
       </c>
       <c r="L57" t="n">
-        <v>0.0004217577979304504</v>
+        <v>0.001771023452725308</v>
       </c>
       <c r="M57" t="n">
-        <v>0.000368693775630591</v>
+        <v>0.001424456895764185</v>
       </c>
       <c r="N57" t="n">
-        <v>0.0004984578215202946</v>
+        <v>0.002893965756722691</v>
       </c>
       <c r="O57" t="n">
-        <v>0.0004500185738535041</v>
+        <v>0.002577105441845946</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0004244644107541152</v>
+        <v>0.002219107116504039</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.0003695371285443526</v>
+        <v>0.001499466149214551</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0004344194938406465</v>
+        <v>0.001328038249429491</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0005935444491544616</v>
+        <v>0.001701332060040773</v>
       </c>
       <c r="T57" t="n">
-        <v>0.0005189069753347839</v>
+        <v>0.001768943160507693</v>
       </c>
       <c r="U57" t="n">
-        <v>0.0005580070907635715</v>
+        <v>0.001810029940423962</v>
       </c>
       <c r="V57" t="n">
-        <v>0.0005926991665286614</v>
+        <v>0.001647706303117631</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0005647696334079814</v>
+        <v>0.001633010570951217</v>
       </c>
       <c r="X57" t="n">
-        <v>0.0005580551416359648</v>
+        <v>0.001593035915528635</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.00071131573563992</v>
+        <v>0.00160957941989414</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.0006801128475512493</v>
+        <v>0.001556980367500327</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.0007898545424566821</v>
+        <v>0.001597861832554039</v>
       </c>
     </row>
     <row r="58">
@@ -5326,83 +5326,83 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>cellular bud</t>
+          <t>cytoplasmic vesicle</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.001884614432021933</v>
+        <v>0.001250169983952636</v>
       </c>
       <c r="D58" t="n">
-        <v>0.002160813469002975</v>
+        <v>0.0008200461541930541</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001899324188642959</v>
+        <v>0.0008438282491590618</v>
       </c>
       <c r="F58" t="n">
-        <v>0.001821548985516648</v>
+        <v>0.0006894249974616438</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00169177362184389</v>
+        <v>0.0006816164974755105</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00147503523328639</v>
+        <v>0.0006490288149046805</v>
       </c>
       <c r="I58" t="n">
-        <v>0.002371854233116223</v>
+        <v>0.0008268548717798111</v>
       </c>
       <c r="J58" t="n">
-        <v>0.002475654425363569</v>
+        <v>0.0009199718182065146</v>
       </c>
       <c r="K58" t="n">
-        <v>0.002030531077052462</v>
+        <v>0.0007108519661356376</v>
       </c>
       <c r="L58" t="n">
-        <v>0.001771023452725308</v>
+        <v>0.0006640749921725772</v>
       </c>
       <c r="M58" t="n">
-        <v>0.001424456895764185</v>
+        <v>0.000589367721643624</v>
       </c>
       <c r="N58" t="n">
-        <v>0.002893965756722691</v>
+        <v>0.001023408009678495</v>
       </c>
       <c r="O58" t="n">
-        <v>0.002577105441845946</v>
+        <v>0.0009216006053303402</v>
       </c>
       <c r="P58" t="n">
-        <v>0.002219107116504039</v>
+        <v>0.0007989485372452324</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001499466149214551</v>
+        <v>0.0005565884169986107</v>
       </c>
       <c r="R58" t="n">
-        <v>0.001328038249429491</v>
+        <v>0.0005602435890346029</v>
       </c>
       <c r="S58" t="n">
-        <v>0.001701332060040773</v>
+        <v>0.001267146953423555</v>
       </c>
       <c r="T58" t="n">
-        <v>0.001768943160507693</v>
+        <v>0.001255879521052049</v>
       </c>
       <c r="U58" t="n">
-        <v>0.001810029940423962</v>
+        <v>0.001282465316649026</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001647706303117631</v>
+        <v>0.001025303799054754</v>
       </c>
       <c r="W58" t="n">
-        <v>0.001633010570951217</v>
+        <v>0.0009364737698073098</v>
       </c>
       <c r="X58" t="n">
-        <v>0.001593035915528635</v>
+        <v>0.0009376575953436199</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.00160957941989414</v>
+        <v>0.001242030237242117</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.001556980367500327</v>
+        <v>0.001233735839310463</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.001597861832554039</v>
+        <v>0.001245535719896503</v>
       </c>
     </row>
     <row r="59">
@@ -5411,83 +5411,83 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>cytoplasmic vesicle</t>
+          <t>endosome</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.001250169983952636</v>
+        <v>0.001892768644873129</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0008200461541930541</v>
+        <v>0.002231271369523163</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0008438282491590618</v>
+        <v>0.002377945542094984</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0006894249974616438</v>
+        <v>0.001853950332927778</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0006816164974755105</v>
+        <v>0.001734607332105092</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0006490288149046805</v>
+        <v>0.001451712986192468</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0008268548717798111</v>
+        <v>0.002110436700850782</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0009199718182065146</v>
+        <v>0.002407967578927267</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0007108519661356376</v>
+        <v>0.001831848660046595</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0006640749921725772</v>
+        <v>0.001581402249491555</v>
       </c>
       <c r="M59" t="n">
-        <v>0.000589367721643624</v>
+        <v>0.001327938048719484</v>
       </c>
       <c r="N59" t="n">
-        <v>0.001023408009678495</v>
+        <v>0.002214230155450045</v>
       </c>
       <c r="O59" t="n">
-        <v>0.0009216006053303402</v>
+        <v>0.002160816228944146</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0007989485372452324</v>
+        <v>0.001949533328633897</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0005565884169986107</v>
+        <v>0.001423908429807543</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0005602435890346029</v>
+        <v>0.001242619596009285</v>
       </c>
       <c r="S59" t="n">
-        <v>0.001267146953423555</v>
+        <v>0.001524924329739448</v>
       </c>
       <c r="T59" t="n">
-        <v>0.001255879521052049</v>
+        <v>0.001601080266812246</v>
       </c>
       <c r="U59" t="n">
-        <v>0.001282465316649026</v>
+        <v>0.001501781741759905</v>
       </c>
       <c r="V59" t="n">
-        <v>0.001025303799054754</v>
+        <v>0.002348102434200156</v>
       </c>
       <c r="W59" t="n">
-        <v>0.0009364737698073098</v>
+        <v>0.002063076084852373</v>
       </c>
       <c r="X59" t="n">
-        <v>0.0009376575953436199</v>
+        <v>0.00198992415611889</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.001242030237242117</v>
+        <v>0.001263566773609428</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.001233735839310463</v>
+        <v>0.001218438283229144</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.001245535719896503</v>
+        <v>0.001262080264243185</v>
       </c>
     </row>
     <row r="60">
@@ -5496,83 +5496,83 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>endosome</t>
+          <t>chromosome, centromeric region</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.001892768644873129</v>
+        <v>0.001047343550408769</v>
       </c>
       <c r="D60" t="n">
-        <v>0.002231271369523163</v>
+        <v>0.0003556822394400022</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002377945542094984</v>
+        <v>0.0003357327494740369</v>
       </c>
       <c r="F60" t="n">
-        <v>0.001853950332927778</v>
+        <v>0.0003967710586584412</v>
       </c>
       <c r="G60" t="n">
-        <v>0.001734607332105092</v>
+        <v>0.0003711700419238734</v>
       </c>
       <c r="H60" t="n">
-        <v>0.001451712986192468</v>
+        <v>0.0003352969805923715</v>
       </c>
       <c r="I60" t="n">
-        <v>0.002110436700850782</v>
+        <v>0.0004081444237852421</v>
       </c>
       <c r="J60" t="n">
-        <v>0.002407967578927267</v>
+        <v>0.000446767780306688</v>
       </c>
       <c r="K60" t="n">
-        <v>0.001831848660046595</v>
+        <v>0.0004315043910470179</v>
       </c>
       <c r="L60" t="n">
-        <v>0.001581402249491555</v>
+        <v>0.0003537821212935545</v>
       </c>
       <c r="M60" t="n">
-        <v>0.001327938048719484</v>
+        <v>0.0002976720855754843</v>
       </c>
       <c r="N60" t="n">
-        <v>0.002214230155450045</v>
+        <v>0.000544169692110637</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002160816228944146</v>
+        <v>0.0005003263631688216</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001949533328633897</v>
+        <v>0.0004943658525900541</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001423908429807543</v>
+        <v>0.0003387708309031309</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001242619596009285</v>
+        <v>0.0003092351211417516</v>
       </c>
       <c r="S60" t="n">
-        <v>0.001524924329739448</v>
+        <v>0.000328640744265256</v>
       </c>
       <c r="T60" t="n">
-        <v>0.001601080266812246</v>
+        <v>0.0003341989312287408</v>
       </c>
       <c r="U60" t="n">
-        <v>0.001501781741759905</v>
+        <v>0.0003341046014761956</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002348102434200156</v>
+        <v>0.0002799038122495608</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002063076084852373</v>
+        <v>0.0002492049217121818</v>
       </c>
       <c r="X60" t="n">
-        <v>0.00198992415611889</v>
+        <v>0.0002475033364342547</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.001263566773609428</v>
+        <v>0.0002620084839731995</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.001218438283229144</v>
+        <v>0.0002558482256617942</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.001262080264243185</v>
+        <v>0.00024693428299664</v>
       </c>
     </row>
     <row r="61">
@@ -5581,83 +5581,83 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>chromosome, centromeric region</t>
+          <t>cortical endoplasmic reticulum</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.001047343550408769</v>
+        <v>0.0004976614759128284</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0003556822394400022</v>
+        <v>0.0006228105018753101</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0003357327494740369</v>
+        <v>0.0005727703008993799</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0003967710586584412</v>
+        <v>0.0003985396468403475</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0003711700419238734</v>
+        <v>0.0003688841124394321</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0003352969805923715</v>
+        <v>0.0003616377833012896</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0004081444237852421</v>
+        <v>0.0006936837778243123</v>
       </c>
       <c r="J61" t="n">
-        <v>0.000446767780306688</v>
+        <v>0.0006682039662594409</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0004315043910470179</v>
+        <v>0.0005171710680627181</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0003537821212935545</v>
+        <v>0.0003908754366461335</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0002976720855754843</v>
+        <v>0.0003511004658504771</v>
       </c>
       <c r="N61" t="n">
-        <v>0.000544169692110637</v>
+        <v>0.0006378411284470749</v>
       </c>
       <c r="O61" t="n">
-        <v>0.0005003263631688216</v>
+        <v>0.0006138383276545735</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0004943658525900541</v>
+        <v>0.0005124278169542725</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.0003387708309031309</v>
+        <v>0.0003768524490184068</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0003092351211417516</v>
+        <v>0.000318602084587334</v>
       </c>
       <c r="S61" t="n">
-        <v>0.000328640744265256</v>
+        <v>0.0005173231833567607</v>
       </c>
       <c r="T61" t="n">
-        <v>0.0003341989312287408</v>
+        <v>0.0004591675863220938</v>
       </c>
       <c r="U61" t="n">
-        <v>0.0003341046014761956</v>
+        <v>0.0004922438136082338</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0002799038122495608</v>
+        <v>0.0004762531591238165</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0002492049217121818</v>
+        <v>0.0005117420466173045</v>
       </c>
       <c r="X61" t="n">
-        <v>0.0002475033364342547</v>
+        <v>0.0004972636849827105</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.0002620084839731995</v>
+        <v>0.0004545719864953552</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.0002558482256617942</v>
+        <v>0.0004272784276820857</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.00024693428299664</v>
+        <v>0.0004410480403603403</v>
       </c>
     </row>
     <row r="62">
@@ -5666,83 +5666,83 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cortical endoplasmic reticulum</t>
+          <t>cytoplasmic stress granule</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.0004976614759128284</v>
+        <v>0.03933920062161234</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0006228105018753101</v>
+        <v>0.03627367548224629</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0005727703008993799</v>
+        <v>0.03777147926596536</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0003985396468403475</v>
+        <v>0.04075370971256539</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0003688841124394321</v>
+        <v>0.04255667843325391</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0003616377833012896</v>
+        <v>0.04413624995647562</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0006936837778243123</v>
+        <v>0.03991166917921923</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0006682039662594409</v>
+        <v>0.04051239290048646</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0005171710680627181</v>
+        <v>0.04481417763261148</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0003908754366461335</v>
+        <v>0.04546044939181281</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0003511004658504771</v>
+        <v>0.0474578797263576</v>
       </c>
       <c r="N62" t="n">
-        <v>0.0006378411284470749</v>
+        <v>0.03379833383003493</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0006138383276545735</v>
+        <v>0.03570074652258518</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0005124278169542725</v>
+        <v>0.03942312773928789</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0003768524490184068</v>
+        <v>0.04736615841978058</v>
       </c>
       <c r="R62" t="n">
-        <v>0.000318602084587334</v>
+        <v>0.04300870373535486</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005173231833567607</v>
+        <v>0.04332918969450009</v>
       </c>
       <c r="T62" t="n">
-        <v>0.0004591675863220938</v>
+        <v>0.04159661586166512</v>
       </c>
       <c r="U62" t="n">
-        <v>0.0004922438136082338</v>
+        <v>0.04154502128448869</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0004762531591238165</v>
+        <v>0.03429656932288957</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0005117420466173045</v>
+        <v>0.03275199044489815</v>
       </c>
       <c r="X62" t="n">
-        <v>0.0004972636849827105</v>
+        <v>0.03053666901632271</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.0004545719864953552</v>
+        <v>0.03169074678127289</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.0004272784276820857</v>
+        <v>0.03255284692584148</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.0004410480403603403</v>
+        <v>0.03282611114493793</v>
       </c>
     </row>
     <row r="63">
@@ -5751,83 +5751,83 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cytoplasmic stress granule</t>
+          <t>late endosome</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.03933920062161234</v>
+        <v>0.0002666014333104617</v>
       </c>
       <c r="D63" t="n">
-        <v>0.03627367548224629</v>
+        <v>0.0002756978094610696</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03777147926596536</v>
+        <v>0.0002522175866335124</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04075370971256539</v>
+        <v>0.0001895110590617316</v>
       </c>
       <c r="G63" t="n">
-        <v>0.04255667843325391</v>
+        <v>0.0001879602528027751</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04413624995647562</v>
+        <v>0.0001536683558909999</v>
       </c>
       <c r="I63" t="n">
-        <v>0.03991166917921923</v>
+        <v>0.0003395210509525789</v>
       </c>
       <c r="J63" t="n">
-        <v>0.04051239290048646</v>
+        <v>0.0003542293629846266</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04481417763261148</v>
+        <v>0.0002871116613309172</v>
       </c>
       <c r="L63" t="n">
-        <v>0.04546044939181281</v>
+        <v>0.0002109270712810698</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0474578797263576</v>
+        <v>0.000168740697759038</v>
       </c>
       <c r="N63" t="n">
-        <v>0.03379833383003493</v>
+        <v>0.0003580957535237042</v>
       </c>
       <c r="O63" t="n">
-        <v>0.03570074652258518</v>
+        <v>0.0003091617066000866</v>
       </c>
       <c r="P63" t="n">
-        <v>0.03942312773928789</v>
+        <v>0.0002627111838061681</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.04736615841978058</v>
+        <v>0.0001602741457562777</v>
       </c>
       <c r="R63" t="n">
-        <v>0.04300870373535486</v>
+        <v>0.0001304909010035522</v>
       </c>
       <c r="S63" t="n">
-        <v>0.04332918969450009</v>
+        <v>0.0002193084202369547</v>
       </c>
       <c r="T63" t="n">
-        <v>0.04159661586166512</v>
+        <v>0.0002035425363254414</v>
       </c>
       <c r="U63" t="n">
-        <v>0.04154502128448869</v>
+        <v>0.0001812784922532281</v>
       </c>
       <c r="V63" t="n">
-        <v>0.03429656932288957</v>
+        <v>0.0002042146716536256</v>
       </c>
       <c r="W63" t="n">
-        <v>0.03275199044489815</v>
+        <v>0.0001997410855689226</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03053666901632271</v>
+        <v>0.0002123675948557939</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.03169074678127289</v>
+        <v>0.0001781115539339662</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.03255284692584148</v>
+        <v>0.000191929856399554</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.03282611114493793</v>
+        <v>0.0002037913620705028</v>
       </c>
     </row>
     <row r="64">
@@ -5836,83 +5836,83 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>late endosome</t>
+          <t>trans-golgi network</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.0002666014333104617</v>
+        <v>0.0007205494597838876</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0002756978094610696</v>
+        <v>0.0004712078905984472</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0002522175866335124</v>
+        <v>0.0005297682470348601</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0001895110590617316</v>
+        <v>0.0005449072341349106</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0001879602528027751</v>
+        <v>0.0005176331912419411</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0001536683558909999</v>
+        <v>0.000486329072376675</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0003395210509525789</v>
+        <v>0.0005389657735564889</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0003542293629846266</v>
+        <v>0.0006116822686300903</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0002871116613309172</v>
+        <v>0.0005268561338230298</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0002109270712810698</v>
+        <v>0.0005354686586301185</v>
       </c>
       <c r="M64" t="n">
-        <v>0.000168740697759038</v>
+        <v>0.0004532063888634188</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0003580957535237042</v>
+        <v>0.0006722282130248468</v>
       </c>
       <c r="O64" t="n">
-        <v>0.0003091617066000866</v>
+        <v>0.0006559410535208858</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0002627111838061681</v>
+        <v>0.0006738857977929003</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0001602741457562777</v>
+        <v>0.0005440812457481219</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0001304909010035522</v>
+        <v>0.0004767070179532774</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0002193084202369547</v>
+        <v>0.0005470824219621293</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0002035425363254414</v>
+        <v>0.0005749804612254783</v>
       </c>
       <c r="U64" t="n">
-        <v>0.0001812784922532281</v>
+        <v>0.0005500100858232107</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0002042146716536256</v>
+        <v>0.0003631351906905705</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0001997410855689226</v>
+        <v>0.00032493670358672</v>
       </c>
       <c r="X64" t="n">
-        <v>0.0002123675948557939</v>
+        <v>0.0003426829658400238</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.0001781115539339662</v>
+        <v>0.0004352500583200458</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.000191929856399554</v>
+        <v>0.0004319826562981701</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.0002037913620705028</v>
+        <v>0.0004375152296277751</v>
       </c>
     </row>
     <row r="65">
@@ -5921,83 +5921,83 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>trans-golgi network</t>
+          <t>mating projection tip</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.0007205494597838876</v>
+        <v>0.01108544061012593</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0004712078905984472</v>
+        <v>0.01183198898577286</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0005297682470348601</v>
+        <v>0.01204047520489829</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0005449072341349106</v>
+        <v>0.01104244534210776</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0005176331912419411</v>
+        <v>0.0109270134891363</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000486329072376675</v>
+        <v>0.01176088307369952</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0005389657735564889</v>
+        <v>0.01128109477134994</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0006116822686300903</v>
+        <v>0.01145016331780394</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0005268561338230298</v>
+        <v>0.01054861389730336</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0005354686586301185</v>
+        <v>0.01098805658734278</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0004532063888634188</v>
+        <v>0.01094386493461197</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0006722282130248468</v>
+        <v>0.0114337815312893</v>
       </c>
       <c r="O65" t="n">
-        <v>0.0006559410535208858</v>
+        <v>0.01074866712059767</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0006738857977929003</v>
+        <v>0.01119754545545858</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.0005440812457481219</v>
+        <v>0.01084309221418272</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0004767070179532774</v>
+        <v>0.01111128680138421</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005470824219621293</v>
+        <v>0.01074841520416974</v>
       </c>
       <c r="T65" t="n">
-        <v>0.0005749804612254783</v>
+        <v>0.01098707759858162</v>
       </c>
       <c r="U65" t="n">
-        <v>0.0005500100858232107</v>
+        <v>0.01065686803439102</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0003631351906905705</v>
+        <v>0.009328931837842072</v>
       </c>
       <c r="W65" t="n">
-        <v>0.00032493670358672</v>
+        <v>0.008647137125337661</v>
       </c>
       <c r="X65" t="n">
-        <v>0.0003426829658400238</v>
+        <v>0.008386259959198778</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.0004352500583200458</v>
+        <v>0.01060567830983805</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.0004319826562981701</v>
+        <v>0.01068070604214875</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.0004375152296277751</v>
+        <v>0.01066025188029692</v>
       </c>
     </row>
     <row r="66">
@@ -6006,83 +6006,83 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>mating projection tip</t>
+          <t>nuclear envelope</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.01108544061012593</v>
+        <v>0.001976521761347008</v>
       </c>
       <c r="D66" t="n">
-        <v>0.01183198898577286</v>
+        <v>0.001347327299131795</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01204047520489829</v>
+        <v>0.001263496304280684</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01104244534210776</v>
+        <v>0.001623806327053751</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0109270134891363</v>
+        <v>0.00161768563462962</v>
       </c>
       <c r="H66" t="n">
-        <v>0.01176088307369952</v>
+        <v>0.00187132530698193</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01128109477134994</v>
+        <v>0.00167151543291827</v>
       </c>
       <c r="J66" t="n">
-        <v>0.01145016331780394</v>
+        <v>0.001610099253668113</v>
       </c>
       <c r="K66" t="n">
-        <v>0.01054861389730336</v>
+        <v>0.001521061652583312</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01098805658734278</v>
+        <v>0.00184899434539048</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01094386493461197</v>
+        <v>0.002034261745417189</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0114337815312893</v>
+        <v>0.00166499642138094</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01074866712059767</v>
+        <v>0.001552651841255761</v>
       </c>
       <c r="P66" t="n">
-        <v>0.01119754545545858</v>
+        <v>0.001676869340114355</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.01084309221418272</v>
+        <v>0.001690905117678844</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01111128680138421</v>
+        <v>0.002142306347991485</v>
       </c>
       <c r="S66" t="n">
-        <v>0.01074841520416974</v>
+        <v>0.001533718625496581</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01098707759858162</v>
+        <v>0.001789780060102576</v>
       </c>
       <c r="U66" t="n">
-        <v>0.01065686803439102</v>
+        <v>0.001654394110231276</v>
       </c>
       <c r="V66" t="n">
-        <v>0.009328931837842072</v>
+        <v>0.001431097440661572</v>
       </c>
       <c r="W66" t="n">
-        <v>0.008647137125337661</v>
+        <v>0.001256115679441104</v>
       </c>
       <c r="X66" t="n">
-        <v>0.008386259959198778</v>
+        <v>0.001227750958228491</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.01060567830983805</v>
+        <v>0.001133005029222928</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.01068070604214875</v>
+        <v>0.001158605183473587</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01066025188029692</v>
+        <v>0.001130376957934992</v>
       </c>
     </row>
     <row r="67">
@@ -6091,83 +6091,83 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nuclear envelope</t>
+          <t>mitochondrion_unassigned</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.001976521761347008</v>
+        <v>0.05645121575691895</v>
       </c>
       <c r="D67" t="n">
-        <v>0.001347327299131795</v>
+        <v>0.05471987784279479</v>
       </c>
       <c r="E67" t="n">
-        <v>0.001263496304280684</v>
+        <v>0.05626198163504247</v>
       </c>
       <c r="F67" t="n">
-        <v>0.001623806327053751</v>
+        <v>0.05730665977699208</v>
       </c>
       <c r="G67" t="n">
-        <v>0.00161768563462962</v>
+        <v>0.05672394053425373</v>
       </c>
       <c r="H67" t="n">
-        <v>0.00187132530698193</v>
+        <v>0.05790514194622767</v>
       </c>
       <c r="I67" t="n">
-        <v>0.00167151543291827</v>
+        <v>0.06363178846993491</v>
       </c>
       <c r="J67" t="n">
-        <v>0.001610099253668113</v>
+        <v>0.06293366861377632</v>
       </c>
       <c r="K67" t="n">
-        <v>0.001521061652583312</v>
+        <v>0.06441313175430827</v>
       </c>
       <c r="L67" t="n">
-        <v>0.00184899434539048</v>
+        <v>0.06404237692784664</v>
       </c>
       <c r="M67" t="n">
-        <v>0.002034261745417189</v>
+        <v>0.06308991697977627</v>
       </c>
       <c r="N67" t="n">
-        <v>0.00166499642138094</v>
+        <v>0.06164748802754788</v>
       </c>
       <c r="O67" t="n">
-        <v>0.001552651841255761</v>
+        <v>0.06225304563269494</v>
       </c>
       <c r="P67" t="n">
-        <v>0.001676869340114355</v>
+        <v>0.0626369500331271</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.001690905117678844</v>
+        <v>0.06231574627721846</v>
       </c>
       <c r="R67" t="n">
-        <v>0.002142306347991485</v>
+        <v>0.05918166836297818</v>
       </c>
       <c r="S67" t="n">
-        <v>0.001533718625496581</v>
+        <v>0.05938396221735375</v>
       </c>
       <c r="T67" t="n">
-        <v>0.001789780060102576</v>
+        <v>0.05943129395832213</v>
       </c>
       <c r="U67" t="n">
-        <v>0.001654394110231276</v>
+        <v>0.06001880169748541</v>
       </c>
       <c r="V67" t="n">
-        <v>0.001431097440661572</v>
+        <v>0.05709237279726317</v>
       </c>
       <c r="W67" t="n">
-        <v>0.001256115679441104</v>
+        <v>0.05251382605689264</v>
       </c>
       <c r="X67" t="n">
-        <v>0.001227750958228491</v>
+        <v>0.05081950513149351</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.001133005029222928</v>
+        <v>0.04555219952718913</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.001158605183473587</v>
+        <v>0.04582670135385025</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.001130376957934992</v>
+        <v>0.0482088369549415</v>
       </c>
     </row>
     <row r="68">
@@ -6176,83 +6176,83 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>mitochondrion_unassigned</t>
+          <t>mitochondrial nucleoid</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.05645121575691895</v>
+        <v>0.02553835490705627</v>
       </c>
       <c r="D68" t="n">
-        <v>0.05471987784279479</v>
+        <v>0.03724295211811118</v>
       </c>
       <c r="E68" t="n">
-        <v>0.05626198163504247</v>
+        <v>0.03860451945682958</v>
       </c>
       <c r="F68" t="n">
-        <v>0.05730665977699208</v>
+        <v>0.03355743343896454</v>
       </c>
       <c r="G68" t="n">
-        <v>0.05672394053425373</v>
+        <v>0.03352092234964911</v>
       </c>
       <c r="H68" t="n">
-        <v>0.05790514194622767</v>
+        <v>0.03077086674333009</v>
       </c>
       <c r="I68" t="n">
-        <v>0.06363178846993491</v>
+        <v>0.02671366586090864</v>
       </c>
       <c r="J68" t="n">
-        <v>0.06293366861377632</v>
+        <v>0.02382071354701341</v>
       </c>
       <c r="K68" t="n">
-        <v>0.06441313175430827</v>
+        <v>0.02399975973781728</v>
       </c>
       <c r="L68" t="n">
-        <v>0.06404237692784664</v>
+        <v>0.02303399366322026</v>
       </c>
       <c r="M68" t="n">
-        <v>0.06308991697977627</v>
+        <v>0.02384027417634396</v>
       </c>
       <c r="N68" t="n">
-        <v>0.06164748802754788</v>
+        <v>0.02607820757125949</v>
       </c>
       <c r="O68" t="n">
-        <v>0.06225304563269494</v>
+        <v>0.02698318585804482</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0626369500331271</v>
+        <v>0.02596671169161352</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.06231574627721846</v>
+        <v>0.02565217060510818</v>
       </c>
       <c r="R68" t="n">
-        <v>0.05918166836297818</v>
+        <v>0.02633969898765819</v>
       </c>
       <c r="S68" t="n">
-        <v>0.05938396221735375</v>
+        <v>0.02641255100406565</v>
       </c>
       <c r="T68" t="n">
-        <v>0.05943129395832213</v>
+        <v>0.02868992116191928</v>
       </c>
       <c r="U68" t="n">
-        <v>0.06001880169748541</v>
+        <v>0.02848395099507278</v>
       </c>
       <c r="V68" t="n">
-        <v>0.05709237279726317</v>
+        <v>0.02267690803885792</v>
       </c>
       <c r="W68" t="n">
-        <v>0.05251382605689264</v>
+        <v>0.02016426219379407</v>
       </c>
       <c r="X68" t="n">
-        <v>0.05081950513149351</v>
+        <v>0.02246833039347259</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.04555219952718913</v>
+        <v>0.03377424670962893</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.04582670135385025</v>
+        <v>0.03412754263582235</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0482088369549415</v>
+        <v>0.0330784212728724</v>
       </c>
     </row>
     <row r="69">
@@ -6261,83 +6261,83 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>mitochondrial nucleoid</t>
+          <t>cellular bud neck septin ring</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.02553835490705627</v>
+        <v>0.0005560207315612355</v>
       </c>
       <c r="D69" t="n">
-        <v>0.03724295211811118</v>
+        <v>0.0006183251406688448</v>
       </c>
       <c r="E69" t="n">
-        <v>0.03860451945682958</v>
+        <v>0.0005531112039920233</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03355743343896454</v>
+        <v>0.0005584078638339758</v>
       </c>
       <c r="G69" t="n">
-        <v>0.03352092234964911</v>
+        <v>0.0004971931649545997</v>
       </c>
       <c r="H69" t="n">
-        <v>0.03077086674333009</v>
+        <v>0.0004906700519648477</v>
       </c>
       <c r="I69" t="n">
-        <v>0.02671366586090864</v>
+        <v>0.0007242748925189998</v>
       </c>
       <c r="J69" t="n">
-        <v>0.02382071354701341</v>
+        <v>0.0006992504277297672</v>
       </c>
       <c r="K69" t="n">
-        <v>0.02399975973781728</v>
+        <v>0.0005547905161668531</v>
       </c>
       <c r="L69" t="n">
-        <v>0.02303399366322026</v>
+        <v>0.0005254451334716901</v>
       </c>
       <c r="M69" t="n">
-        <v>0.02384027417634396</v>
+        <v>0.0004986976921681049</v>
       </c>
       <c r="N69" t="n">
-        <v>0.02607820757125949</v>
+        <v>0.0008677807917434382</v>
       </c>
       <c r="O69" t="n">
-        <v>0.02698318585804482</v>
+        <v>0.0007585719284212879</v>
       </c>
       <c r="P69" t="n">
-        <v>0.02596671169161352</v>
+        <v>0.0006485231098350713</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.02565217060510818</v>
+        <v>0.0004905776533898521</v>
       </c>
       <c r="R69" t="n">
-        <v>0.02633969898765819</v>
+        <v>0.0004601348694049906</v>
       </c>
       <c r="S69" t="n">
-        <v>0.02641255100406565</v>
+        <v>0.0005021528791232687</v>
       </c>
       <c r="T69" t="n">
-        <v>0.02868992116191928</v>
+        <v>0.0004838663164876835</v>
       </c>
       <c r="U69" t="n">
-        <v>0.02848395099507278</v>
+        <v>0.0004822110619174225</v>
       </c>
       <c r="V69" t="n">
-        <v>0.02267690803885792</v>
+        <v>0.000454109414319979</v>
       </c>
       <c r="W69" t="n">
-        <v>0.02016426219379407</v>
+        <v>0.0004493780806638857</v>
       </c>
       <c r="X69" t="n">
-        <v>0.02246833039347259</v>
+        <v>0.000513143428499887</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.03377424670962893</v>
+        <v>0.0006086661681272267</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.03412754263582235</v>
+        <v>0.0005849712458332529</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.0330784212728724</v>
+        <v>0.0005873902882363457</v>
       </c>
     </row>
     <row r="70">
@@ -6346,83 +6346,83 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>cellular bud neck septin ring</t>
+          <t>cellular bud tip</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.0005560207315612355</v>
+        <v>0.003758318622163938</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0006183251406688448</v>
+        <v>0.004031814166913348</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0005531112039920233</v>
+        <v>0.003857417263955584</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0005584078638339758</v>
+        <v>0.003664745194684894</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0004971931649545997</v>
+        <v>0.003423049873526169</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0004906700519648477</v>
+        <v>0.003260945326102867</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0007242748925189998</v>
+        <v>0.004350419814636033</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0006992504277297672</v>
+        <v>0.004377199063979628</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0005547905161668531</v>
+        <v>0.003737991962095026</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0005254451334716901</v>
+        <v>0.003500054227587991</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0004986976921681049</v>
+        <v>0.002931525826336962</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0008677807917434382</v>
+        <v>0.004980833498090269</v>
       </c>
       <c r="O70" t="n">
-        <v>0.0007585719284212879</v>
+        <v>0.004527328665297578</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0006485231098350713</v>
+        <v>0.004172107395306957</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.0004905776533898521</v>
+        <v>0.003110296732728779</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0004601348694049906</v>
+        <v>0.00303283228428824</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0005021528791232687</v>
+        <v>0.003593694306559932</v>
       </c>
       <c r="T70" t="n">
-        <v>0.0004838663164876835</v>
+        <v>0.003575643776027389</v>
       </c>
       <c r="U70" t="n">
-        <v>0.0004822110619174225</v>
+        <v>0.003503462576672695</v>
       </c>
       <c r="V70" t="n">
-        <v>0.000454109414319979</v>
+        <v>0.003221576836708161</v>
       </c>
       <c r="W70" t="n">
-        <v>0.0004493780806638857</v>
+        <v>0.003115319974763072</v>
       </c>
       <c r="X70" t="n">
-        <v>0.000513143428499887</v>
+        <v>0.003107926052317684</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.0006086661681272267</v>
+        <v>0.003379077768717308</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.0005849712458332529</v>
+        <v>0.003222518683387964</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.0005873902882363457</v>
+        <v>0.003279951746427265</v>
       </c>
     </row>
     <row r="71">
@@ -6431,83 +6431,83 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cellular bud tip</t>
+          <t>nuclear periphery</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.003758318622163938</v>
+        <v>0.002572476121920987</v>
       </c>
       <c r="D71" t="n">
-        <v>0.004031814166913348</v>
+        <v>0.002920291197086757</v>
       </c>
       <c r="E71" t="n">
-        <v>0.003857417263955584</v>
+        <v>0.002844709104104256</v>
       </c>
       <c r="F71" t="n">
-        <v>0.003664745194684894</v>
+        <v>0.001958204029298033</v>
       </c>
       <c r="G71" t="n">
-        <v>0.003423049873526169</v>
+        <v>0.002006385787593214</v>
       </c>
       <c r="H71" t="n">
-        <v>0.003260945326102867</v>
+        <v>0.001985175696436764</v>
       </c>
       <c r="I71" t="n">
-        <v>0.004350419814636033</v>
+        <v>0.004500417653358465</v>
       </c>
       <c r="J71" t="n">
-        <v>0.004377199063979628</v>
+        <v>0.004009419767575176</v>
       </c>
       <c r="K71" t="n">
-        <v>0.003737991962095026</v>
+        <v>0.003555803202240622</v>
       </c>
       <c r="L71" t="n">
-        <v>0.003500054227587991</v>
+        <v>0.003200534141523657</v>
       </c>
       <c r="M71" t="n">
-        <v>0.002931525826336962</v>
+        <v>0.003254362780929652</v>
       </c>
       <c r="N71" t="n">
-        <v>0.004980833498090269</v>
+        <v>0.002311581041453418</v>
       </c>
       <c r="O71" t="n">
-        <v>0.004527328665297578</v>
+        <v>0.002189247946594841</v>
       </c>
       <c r="P71" t="n">
-        <v>0.004172107395306957</v>
+        <v>0.002085555038615209</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.003110296732728779</v>
+        <v>0.002010576445891971</v>
       </c>
       <c r="R71" t="n">
-        <v>0.00303283228428824</v>
+        <v>0.0019733589501373</v>
       </c>
       <c r="S71" t="n">
-        <v>0.003593694306559932</v>
+        <v>0.002706372187546149</v>
       </c>
       <c r="T71" t="n">
-        <v>0.003575643776027389</v>
+        <v>0.002722246613861032</v>
       </c>
       <c r="U71" t="n">
-        <v>0.003503462576672695</v>
+        <v>0.002626727076000367</v>
       </c>
       <c r="V71" t="n">
-        <v>0.003221576836708161</v>
+        <v>0.003000531351235691</v>
       </c>
       <c r="W71" t="n">
-        <v>0.003115319974763072</v>
+        <v>0.002981115720207195</v>
       </c>
       <c r="X71" t="n">
-        <v>0.003107926052317684</v>
+        <v>0.003011636599462998</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.003379077768717308</v>
+        <v>0.002138720689350111</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.003222518683387964</v>
+        <v>0.002095935043164156</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.003279951746427265</v>
+        <v>0.002174959606750633</v>
       </c>
     </row>
     <row r="72">
@@ -6516,83 +6516,83 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nuclear periphery</t>
+          <t>cell periphery</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.002572476121920987</v>
+        <v>0.009225371755636071</v>
       </c>
       <c r="D72" t="n">
-        <v>0.002920291197086757</v>
+        <v>0.005559994190301709</v>
       </c>
       <c r="E72" t="n">
-        <v>0.002844709104104256</v>
+        <v>0.005424008296646915</v>
       </c>
       <c r="F72" t="n">
-        <v>0.001958204029298033</v>
+        <v>0.005652217579536202</v>
       </c>
       <c r="G72" t="n">
-        <v>0.002006385787593214</v>
+        <v>0.005678796353083443</v>
       </c>
       <c r="H72" t="n">
-        <v>0.001985175696436764</v>
+        <v>0.00536624043259975</v>
       </c>
       <c r="I72" t="n">
-        <v>0.004500417653358465</v>
+        <v>0.005903202549128512</v>
       </c>
       <c r="J72" t="n">
-        <v>0.004009419767575176</v>
+        <v>0.005897417707985033</v>
       </c>
       <c r="K72" t="n">
-        <v>0.003555803202240622</v>
+        <v>0.005848094288827651</v>
       </c>
       <c r="L72" t="n">
-        <v>0.003200534141523657</v>
+        <v>0.00589306012058808</v>
       </c>
       <c r="M72" t="n">
-        <v>0.003254362780929652</v>
+        <v>0.005599317075718458</v>
       </c>
       <c r="N72" t="n">
-        <v>0.002311581041453418</v>
+        <v>0.005514575398880072</v>
       </c>
       <c r="O72" t="n">
-        <v>0.002189247946594841</v>
+        <v>0.005398219017418843</v>
       </c>
       <c r="P72" t="n">
-        <v>0.002085555038615209</v>
+        <v>0.005381832366923334</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.002010576445891971</v>
+        <v>0.005110864987136525</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0019733589501373</v>
+        <v>0.005015799198061392</v>
       </c>
       <c r="S72" t="n">
-        <v>0.002706372187546149</v>
+        <v>0.006246977942956583</v>
       </c>
       <c r="T72" t="n">
-        <v>0.002722246613861032</v>
+        <v>0.005766612344553307</v>
       </c>
       <c r="U72" t="n">
-        <v>0.002626727076000367</v>
+        <v>0.005970088251174663</v>
       </c>
       <c r="V72" t="n">
-        <v>0.003000531351235691</v>
+        <v>0.005812737939784519</v>
       </c>
       <c r="W72" t="n">
-        <v>0.002981115720207195</v>
+        <v>0.005938941529718679</v>
       </c>
       <c r="X72" t="n">
-        <v>0.003011636599462998</v>
+        <v>0.005548587511357355</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.002138720689350111</v>
+        <v>0.004364201293706362</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.002095935043164156</v>
+        <v>0.004290280016180581</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.002174959606750633</v>
+        <v>0.004581520619804328</v>
       </c>
     </row>
     <row r="73">
@@ -6601,83 +6601,83 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>cell periphery</t>
+          <t>prospore membrane</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.009225371755636071</v>
+        <v>0.001169642516587751</v>
       </c>
       <c r="D73" t="n">
-        <v>0.005559994190301709</v>
+        <v>0.001239479676274556</v>
       </c>
       <c r="E73" t="n">
-        <v>0.005424008296646915</v>
+        <v>0.00115711752813517</v>
       </c>
       <c r="F73" t="n">
-        <v>0.005652217579536202</v>
+        <v>0.001183275855992886</v>
       </c>
       <c r="G73" t="n">
-        <v>0.005678796353083443</v>
+        <v>0.00104606642808206</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00536624043259975</v>
+        <v>0.001026782415513417</v>
       </c>
       <c r="I73" t="n">
-        <v>0.005903202549128512</v>
+        <v>0.001506608047734459</v>
       </c>
       <c r="J73" t="n">
-        <v>0.005897417707985033</v>
+        <v>0.001600582765878029</v>
       </c>
       <c r="K73" t="n">
-        <v>0.005848094288827651</v>
+        <v>0.001254636714361019</v>
       </c>
       <c r="L73" t="n">
-        <v>0.00589306012058808</v>
+        <v>0.00118800688918107</v>
       </c>
       <c r="M73" t="n">
-        <v>0.005599317075718458</v>
+        <v>0.001061076775736352</v>
       </c>
       <c r="N73" t="n">
-        <v>0.005514575398880072</v>
+        <v>0.001809087154450204</v>
       </c>
       <c r="O73" t="n">
-        <v>0.005398219017418843</v>
+        <v>0.001585597375817572</v>
       </c>
       <c r="P73" t="n">
-        <v>0.005381832366923334</v>
+        <v>0.001368119923922321</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.005110864987136525</v>
+        <v>0.001015897419776433</v>
       </c>
       <c r="R73" t="n">
-        <v>0.005015799198061392</v>
+        <v>0.0009708538519587895</v>
       </c>
       <c r="S73" t="n">
-        <v>0.006246977942956583</v>
+        <v>0.001025048318867592</v>
       </c>
       <c r="T73" t="n">
-        <v>0.005766612344553307</v>
+        <v>0.0009521026373001539</v>
       </c>
       <c r="U73" t="n">
-        <v>0.005970088251174663</v>
+        <v>0.0009370455174353485</v>
       </c>
       <c r="V73" t="n">
-        <v>0.005812737939784519</v>
+        <v>0.0009092455713325585</v>
       </c>
       <c r="W73" t="n">
-        <v>0.005938941529718679</v>
+        <v>0.0009046499569009703</v>
       </c>
       <c r="X73" t="n">
-        <v>0.005548587511357355</v>
+        <v>0.001020033702716614</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.004364201293706362</v>
+        <v>0.001062090474136231</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.004290280016180581</v>
+        <v>0.001007408853110962</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.004581520619804328</v>
+        <v>0.001034137584064133</v>
       </c>
     </row>
     <row r="74">
@@ -6686,83 +6686,83 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>prospore membrane</t>
+          <t>cellular bud neck contractile ring</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.001169642516587751</v>
+        <v>0.00468011457706255</v>
       </c>
       <c r="D74" t="n">
-        <v>0.001239479676274556</v>
+        <v>0.005739747572301212</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00115711752813517</v>
+        <v>0.005224676061939967</v>
       </c>
       <c r="F74" t="n">
-        <v>0.001183275855992886</v>
+        <v>0.005056267205951458</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00104606642808206</v>
+        <v>0.00443791440913315</v>
       </c>
       <c r="H74" t="n">
-        <v>0.001026782415513417</v>
+        <v>0.004361572222851602</v>
       </c>
       <c r="I74" t="n">
-        <v>0.001506608047734459</v>
+        <v>0.006709111140103867</v>
       </c>
       <c r="J74" t="n">
-        <v>0.001600582765878029</v>
+        <v>0.006340153222377835</v>
       </c>
       <c r="K74" t="n">
-        <v>0.001254636714361019</v>
+        <v>0.005546887253421603</v>
       </c>
       <c r="L74" t="n">
-        <v>0.00118800688918107</v>
+        <v>0.003750303599311027</v>
       </c>
       <c r="M74" t="n">
-        <v>0.001061076775736352</v>
+        <v>0.003738087509078372</v>
       </c>
       <c r="N74" t="n">
-        <v>0.001809087154450204</v>
+        <v>0.006818174264401364</v>
       </c>
       <c r="O74" t="n">
-        <v>0.001585597375817572</v>
+        <v>0.006740925422685049</v>
       </c>
       <c r="P74" t="n">
-        <v>0.001368119923922321</v>
+        <v>0.005526085779843221</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.001015897419776433</v>
+        <v>0.004904368455377371</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0009708538519587895</v>
+        <v>0.003806194378193313</v>
       </c>
       <c r="S74" t="n">
-        <v>0.001025048318867592</v>
+        <v>0.004749529600564126</v>
       </c>
       <c r="T74" t="n">
-        <v>0.0009521026373001539</v>
+        <v>0.005181304036997489</v>
       </c>
       <c r="U74" t="n">
-        <v>0.0009370455174353485</v>
+        <v>0.005027121548873306</v>
       </c>
       <c r="V74" t="n">
-        <v>0.0009092455713325585</v>
+        <v>0.00395793670079803</v>
       </c>
       <c r="W74" t="n">
-        <v>0.0009046499569009703</v>
+        <v>0.003442191342071119</v>
       </c>
       <c r="X74" t="n">
-        <v>0.001020033702716614</v>
+        <v>0.003577309480686325</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.001062090474136231</v>
+        <v>0.004585310557145467</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.001007408853110962</v>
+        <v>0.004850364913244783</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.001034137584064133</v>
+        <v>0.004604882849236084</v>
       </c>
     </row>
     <row r="75">
@@ -6771,83 +6771,83 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cellular bud neck contractile ring</t>
+          <t>incipient cellular bud site</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.00468011457706255</v>
+        <v>0.001777877075449255</v>
       </c>
       <c r="D75" t="n">
-        <v>0.005739747572301212</v>
+        <v>0.001758975555099348</v>
       </c>
       <c r="E75" t="n">
-        <v>0.005224676061939967</v>
+        <v>0.00169736274127446</v>
       </c>
       <c r="F75" t="n">
-        <v>0.005056267205951458</v>
+        <v>0.001629964914313506</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00443791440913315</v>
+        <v>0.001516530398797878</v>
       </c>
       <c r="H75" t="n">
-        <v>0.004361572222851602</v>
+        <v>0.001361829814057953</v>
       </c>
       <c r="I75" t="n">
-        <v>0.006709111140103867</v>
+        <v>0.00197913145198261</v>
       </c>
       <c r="J75" t="n">
-        <v>0.006340153222377835</v>
+        <v>0.001911703907501812</v>
       </c>
       <c r="K75" t="n">
-        <v>0.005546887253421603</v>
+        <v>0.001742121552092758</v>
       </c>
       <c r="L75" t="n">
-        <v>0.003750303599311027</v>
+        <v>0.001602968684693908</v>
       </c>
       <c r="M75" t="n">
-        <v>0.003738087509078372</v>
+        <v>0.001437807616301327</v>
       </c>
       <c r="N75" t="n">
-        <v>0.006818174264401364</v>
+        <v>0.002202294057711586</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006740925422685049</v>
+        <v>0.002040621653000015</v>
       </c>
       <c r="P75" t="n">
-        <v>0.005526085779843221</v>
+        <v>0.001887714041546145</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004904368455377371</v>
+        <v>0.001316977147113266</v>
       </c>
       <c r="R75" t="n">
-        <v>0.003806194378193313</v>
+        <v>0.001270226519076242</v>
       </c>
       <c r="S75" t="n">
-        <v>0.004749529600564126</v>
+        <v>0.0011773102944227</v>
       </c>
       <c r="T75" t="n">
-        <v>0.005181304036997489</v>
+        <v>0.001188651229234059</v>
       </c>
       <c r="U75" t="n">
-        <v>0.005027121548873306</v>
+        <v>0.00113234875020382</v>
       </c>
       <c r="V75" t="n">
-        <v>0.00395793670079803</v>
+        <v>0.001002267512743648</v>
       </c>
       <c r="W75" t="n">
-        <v>0.003442191342071119</v>
+        <v>0.0009590205520674691</v>
       </c>
       <c r="X75" t="n">
-        <v>0.003577309480686325</v>
+        <v>0.00102120339055074</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.004585310557145467</v>
+        <v>0.001188820873010355</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.004850364913244783</v>
+        <v>0.001159161841760044</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.004604882849236084</v>
+        <v>0.001198793723396928</v>
       </c>
     </row>
     <row r="76">
@@ -6856,83 +6856,83 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>incipient cellular bud site</t>
+          <t>nucleus-vacuole junction</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.001777877075449255</v>
+        <v>0.0004412108432999502</v>
       </c>
       <c r="D76" t="n">
-        <v>0.001758975555099348</v>
+        <v>0.0004578161032691156</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00169736274127446</v>
+        <v>0.000434996471106719</v>
       </c>
       <c r="F76" t="n">
-        <v>0.001629964914313506</v>
+        <v>0.0003888435141646056</v>
       </c>
       <c r="G76" t="n">
-        <v>0.001516530398797878</v>
+        <v>0.0003754312105975855</v>
       </c>
       <c r="H76" t="n">
-        <v>0.001361829814057953</v>
+        <v>0.0003616995307133818</v>
       </c>
       <c r="I76" t="n">
-        <v>0.00197913145198261</v>
+        <v>0.000632359582849502</v>
       </c>
       <c r="J76" t="n">
-        <v>0.001911703907501812</v>
+        <v>0.0006619841711610919</v>
       </c>
       <c r="K76" t="n">
-        <v>0.001742121552092758</v>
+        <v>0.0004927840199385219</v>
       </c>
       <c r="L76" t="n">
-        <v>0.001602968684693908</v>
+        <v>0.0004274085745904484</v>
       </c>
       <c r="M76" t="n">
-        <v>0.001437807616301327</v>
+        <v>0.0003883012579109577</v>
       </c>
       <c r="N76" t="n">
-        <v>0.002202294057711586</v>
+        <v>0.0006129942269010513</v>
       </c>
       <c r="O76" t="n">
-        <v>0.002040621653000015</v>
+        <v>0.0005836425485952882</v>
       </c>
       <c r="P76" t="n">
-        <v>0.001887714041546145</v>
+        <v>0.0005118165604536148</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.001316977147113266</v>
+        <v>0.0003936380689655457</v>
       </c>
       <c r="R76" t="n">
-        <v>0.001270226519076242</v>
+        <v>0.0003939782741937412</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0011773102944227</v>
+        <v>0.0004913558373260471</v>
       </c>
       <c r="T76" t="n">
-        <v>0.001188651229234059</v>
+        <v>0.0004285535676729958</v>
       </c>
       <c r="U76" t="n">
-        <v>0.00113234875020382</v>
+        <v>0.0004416903423480843</v>
       </c>
       <c r="V76" t="n">
-        <v>0.001002267512743648</v>
+        <v>0.0003380821483562358</v>
       </c>
       <c r="W76" t="n">
-        <v>0.0009590205520674691</v>
+        <v>0.0003861410906051927</v>
       </c>
       <c r="X76" t="n">
-        <v>0.00102120339055074</v>
+        <v>0.0003790527300486487</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.001188820873010355</v>
+        <v>0.0003869503128455457</v>
       </c>
       <c r="Z76" t="n">
-        <v>0.001159161841760044</v>
+        <v>0.0003762947933451421</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.001198793723396928</v>
+        <v>0.0003919398383482767</v>
       </c>
     </row>
     <row r="77">
@@ -6941,83 +6941,83 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nucleus-vacuole junction</t>
+          <t>nuclear replication fork</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.0004412108432999502</v>
+        <v>0.0001749212581777815</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0004578161032691156</v>
+        <v>1.419658040250187e-05</v>
       </c>
       <c r="E77" t="n">
-        <v>0.000434996471106719</v>
+        <v>1.444236648230084e-05</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0003888435141646056</v>
+        <v>1.226600937562683e-05</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0003754312105975855</v>
+        <v>1.256847103550214e-05</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0003616995307133818</v>
+        <v>1.231879219672318e-05</v>
       </c>
       <c r="I77" t="n">
-        <v>0.000632359582849502</v>
+        <v>1.497737487233443e-05</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0006619841711610919</v>
+        <v>1.5269578826484e-05</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0004927840199385219</v>
+        <v>1.386080304751873e-05</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0004274085745904484</v>
+        <v>1.244657170470085e-05</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0003883012579109577</v>
+        <v>1.208458104045975e-05</v>
       </c>
       <c r="N77" t="n">
-        <v>0.0006129942269010513</v>
+        <v>1.290184495594334e-05</v>
       </c>
       <c r="O77" t="n">
-        <v>0.0005836425485952882</v>
+        <v>1.261126551218044e-05</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0005118165604536148</v>
+        <v>1.374625448648398e-05</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0003936380689655457</v>
+        <v>1.11568254467146e-05</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003939782741937412</v>
+        <v>1.129647463700063e-05</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0004913558373260471</v>
+        <v>3.696570904761601e-05</v>
       </c>
       <c r="T77" t="n">
-        <v>0.0004285535676729958</v>
+        <v>4.122521827656388e-05</v>
       </c>
       <c r="U77" t="n">
-        <v>0.0004416903423480843</v>
+        <v>3.944826773732833e-05</v>
       </c>
       <c r="V77" t="n">
-        <v>0.0003380821483562358</v>
+        <v>2.980437564913918e-05</v>
       </c>
       <c r="W77" t="n">
-        <v>0.0003861410906051927</v>
+        <v>3.125265668143246e-05</v>
       </c>
       <c r="X77" t="n">
-        <v>0.0003790527300486487</v>
+        <v>2.634102652267362e-05</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.0003869503128455457</v>
+        <v>2.716163311221721e-05</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.0003762947933451421</v>
+        <v>2.782720714113913e-05</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.0003919398383482767</v>
+        <v>3.315096485352809e-05</v>
       </c>
     </row>
     <row r="78">
@@ -7026,83 +7026,83 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nuclear replication fork</t>
+          <t>early endosome</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.0001749212581777815</v>
+        <v>0.0003215028564577688</v>
       </c>
       <c r="D78" t="n">
-        <v>1.419658040250187e-05</v>
+        <v>0.0003552544068317121</v>
       </c>
       <c r="E78" t="n">
-        <v>1.444236648230084e-05</v>
+        <v>0.0003123916957059662</v>
       </c>
       <c r="F78" t="n">
-        <v>1.226600937562683e-05</v>
+        <v>0.0002819436500502024</v>
       </c>
       <c r="G78" t="n">
-        <v>1.256847103550214e-05</v>
+        <v>0.0002708868779806184</v>
       </c>
       <c r="H78" t="n">
-        <v>1.231879219672318e-05</v>
+        <v>0.0002422900854972905</v>
       </c>
       <c r="I78" t="n">
-        <v>1.497737487233443e-05</v>
+        <v>0.000560083214214049</v>
       </c>
       <c r="J78" t="n">
-        <v>1.5269578826484e-05</v>
+        <v>0.0005718069791127618</v>
       </c>
       <c r="K78" t="n">
-        <v>1.386080304751873e-05</v>
+        <v>0.0003886275650790661</v>
       </c>
       <c r="L78" t="n">
-        <v>1.244657170470085e-05</v>
+        <v>0.0002974729247564647</v>
       </c>
       <c r="M78" t="n">
-        <v>1.208458104045975e-05</v>
+        <v>0.0002562280581436159</v>
       </c>
       <c r="N78" t="n">
-        <v>1.290184495594334e-05</v>
+        <v>0.0004634690456921923</v>
       </c>
       <c r="O78" t="n">
-        <v>1.261126551218044e-05</v>
+        <v>0.0004373583977781284</v>
       </c>
       <c r="P78" t="n">
-        <v>1.374625448648398e-05</v>
+        <v>0.0003634723751187431</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.11568254467146e-05</v>
+        <v>0.0002559076009040636</v>
       </c>
       <c r="R78" t="n">
-        <v>1.129647463700063e-05</v>
+        <v>0.0002314699071654004</v>
       </c>
       <c r="S78" t="n">
-        <v>3.696570904761601e-05</v>
+        <v>0.0003269609124974204</v>
       </c>
       <c r="T78" t="n">
-        <v>4.122521827656388e-05</v>
+        <v>0.0002861121375697771</v>
       </c>
       <c r="U78" t="n">
-        <v>3.944826773732833e-05</v>
+        <v>0.0003036529707952753</v>
       </c>
       <c r="V78" t="n">
-        <v>2.980437564913918e-05</v>
+        <v>0.0002819379288838022</v>
       </c>
       <c r="W78" t="n">
-        <v>3.125265668143246e-05</v>
+        <v>0.0003194500174740175</v>
       </c>
       <c r="X78" t="n">
-        <v>2.634102652267362e-05</v>
+        <v>0.0003009654654920369</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.716163311221721e-05</v>
+        <v>0.0002942422304399895</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.782720714113913e-05</v>
+        <v>0.0002882819748031183</v>
       </c>
       <c r="AA78" t="n">
-        <v>3.315096485352809e-05</v>
+        <v>0.0003009104988427787</v>
       </c>
     </row>
     <row r="79">
@@ -7111,167 +7111,82 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>early endosome</t>
+          <t>site of polarized growth</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.0003215028564577688</v>
+        <v>0.0004071501719422466</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0003552544068317121</v>
+        <v>0.0004325024824643737</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0003123916957059662</v>
+        <v>0.0004736513608473032</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0002819436500502024</v>
+        <v>0.0003802129312006761</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0002708868779806184</v>
+        <v>0.0003866640582569924</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0002422900854972905</v>
+        <v>0.0003584236778756649</v>
       </c>
       <c r="I79" t="n">
-        <v>0.000560083214214049</v>
+        <v>0.0005057938908894476</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0005718069791127618</v>
+        <v>0.0005076564744969622</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0003886275650790661</v>
+        <v>0.0004473156441716274</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0002974729247564647</v>
+        <v>0.0003450963384087463</v>
       </c>
       <c r="M79" t="n">
-        <v>0.0002562280581436159</v>
+        <v>0.0003380825331179327</v>
       </c>
       <c r="N79" t="n">
-        <v>0.0004634690456921923</v>
+        <v>0.0005060195937155895</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0004373583977781284</v>
+        <v>0.0004713069828954117</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0003634723751187431</v>
+        <v>0.000479505778518018</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.0002559076009040636</v>
+        <v>0.000352084518286664</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0002314699071654004</v>
+        <v>0.0003124910392619573</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0003269609124974204</v>
+        <v>0.0004015100661031931</v>
       </c>
       <c r="T79" t="n">
-        <v>0.0002861121375697771</v>
+        <v>0.000365245133432487</v>
       </c>
       <c r="U79" t="n">
-        <v>0.0003036529707952753</v>
+        <v>0.0003447191438869362</v>
       </c>
       <c r="V79" t="n">
-        <v>0.0002819379288838022</v>
+        <v>0.000295976085245973</v>
       </c>
       <c r="W79" t="n">
-        <v>0.0003194500174740175</v>
+        <v>0.0002825283235335271</v>
       </c>
       <c r="X79" t="n">
-        <v>0.0003009654654920369</v>
+        <v>0.0003044890213756572</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.0002942422304399895</v>
+        <v>0.0003358261355523164</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.0002882819748031183</v>
+        <v>0.0003253139076011009</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.0003009104988427787</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>site of polarized growth</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.0004071501719422466</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.0004325024824643737</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.0004736513608473032</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.0003802129312006761</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.0003866640582569924</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0003584236778756649</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.0005057938908894476</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.0005076564744969622</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.0004473156441716274</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0.0003450963384087463</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.0003380825331179327</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.0005060195937155895</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0.0004713069828954117</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0.000479505778518018</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0.000352084518286664</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.0003124910392619573</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0.0004015100661031931</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0.000365245133432487</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0.0003447191438869362</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0.000295976085245973</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0.0002825283235335271</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0.0003044890213756572</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0.0003358261355523164</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0.0003253139076011009</v>
-      </c>
-      <c r="AA80" t="n">
         <v>0.0003238465038970653</v>
       </c>
     </row>
